--- a/data/vsd_records.xlsx
+++ b/data/vsd_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z404"/>
+  <dimension ref="A1:Z468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:50</t>
+          <t>04/06/2026 13:22:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:50</t>
+          <t>04/06/2026 13:22:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:50</t>
+          <t>04/06/2026 13:22:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:51</t>
+          <t>04/06/2026 13:22:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:52</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:53</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:54</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:55</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:25</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:56</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:26</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:57</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:27</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:58</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -13911,7 +13911,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:28</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>04/06/2026 11:17:59</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:00</t>
+          <t>04/06/2026 13:22:29</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -16625,7 +16625,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:01</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -17546,7 +17546,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:30</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:31</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:31</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -17889,7 +17889,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:31</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -18007,7 +18007,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:31</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:31</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:31</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:31</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -18479,7 +18479,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:31</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>04/06/2026 11:18:02</t>
+          <t>04/06/2026 13:22:31</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -19798,14 +19798,10 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 4.400.410,959 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 28/6/2026 là ngày nghỉ)</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 (do ngày 28/6/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 1 trái phiếu được nhận 4.400.410,959 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 28/6/2026 là ngày nghỉ)</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
@@ -19817,28 +19813,18 @@
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
-      <c r="T177" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U177" t="n">
-        <v>4400410959</v>
-      </c>
-      <c r="V177" t="n">
-        <v>8.824999999999999</v>
-      </c>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
       <c r="W177" t="inlineStr"/>
       <c r="X177" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 4.400.410,959 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 28/6/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 1 trái phiếu được nhận 4.400.410,959 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 28/6/2026 là ngày nghỉ)</t>
+          <t>29/6/2026 (do ngày 28/6/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 1 trái phiếu được nhận 4.400.410,959 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 28/6/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 1 trái phiếu được nhận 4.400.410,959 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 28/6/2026 là ngày nghỉ)</t>
         </is>
       </c>
       <c r="Y177" t="n">
@@ -19908,14 +19894,10 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 là ngày nghỉ)</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 (do ngày 27/6/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 1 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 là ngày nghỉ)</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
@@ -19927,28 +19909,18 @@
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>27/06/2026</t>
-        </is>
-      </c>
+      <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr"/>
-      <c r="T178" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U178" t="n">
-        <v>5235616438</v>
-      </c>
-      <c r="V178" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
       <c r="W178" t="inlineStr"/>
       <c r="X178" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 1 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 là ngày nghỉ)</t>
+          <t>29/6/2026 (do ngày 27/6/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 1 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 1 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 là ngày nghỉ)</t>
         </is>
       </c>
       <c r="Y178" t="n">
@@ -20024,7 +19996,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 16/6/2026</t>
+          <t>16/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 16/6/2026</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -20060,7 +20032,7 @@
       <c r="W179" t="inlineStr"/>
       <c r="X179" t="inlineStr">
         <is>
-          <t>Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 16/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 16/6/2026</t>
+          <t>16/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 16/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 16/6/2026</t>
         </is>
       </c>
       <c r="Y179" t="n">
@@ -20129,14 +20101,10 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 58.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc).</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc). - Tỷ lệ thực hiện:01 trái phiếu được nhận 58.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc).</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
@@ -20148,28 +20116,18 @@
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
-      <c r="T180" t="n">
-        <v>1</v>
-      </c>
-      <c r="U180" t="n">
-        <v>58300000</v>
-      </c>
-      <c r="V180" t="n">
-        <v>583000</v>
-      </c>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
       <c r="W180" t="inlineStr"/>
       <c r="X180" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 58.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc). - Tỷ lệ thực hiện:01 trái phiếu được nhận 58.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc).</t>
+          <t>29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc). - Tỷ lệ thực hiện:01 trái phiếu được nhận 58.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc). - Tỷ lệ thực hiện:01 trái phiếu được nhận 58.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc).</t>
         </is>
       </c>
       <c r="Y180" t="n">
@@ -20302,14 +20260,10 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>01 (một) trái phiếu được nhận 6.158.082,192 đồng. - Ngày thanh toán: 29/06/2026 (Do ngày thanh toán không phải là ngày làm việc nên TCĐKCK sẽ thanh toán vào ngày làm việc ngay sau ngày đó)</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/06/2026 (Do ngày thanh toán không phải là ngày làm việc nên TCĐKCK sẽ thanh toán vào ngày làm việc ngay sau ngày đó) - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 6.158.082,192 đồng. - Ngày thanh toán: 29/06/2026 (Do ngày thanh toán không phải là ngày làm việc nên TCĐKCK sẽ thanh toán vào ngày làm việc ngay sau ngày đó)</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
@@ -20321,28 +20275,18 @@
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
+      <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr"/>
-      <c r="T182" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U182" t="n">
-        <v>6158082192</v>
-      </c>
-      <c r="V182" t="n">
-        <v>61580.82192</v>
-      </c>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
       <c r="W182" t="inlineStr"/>
       <c r="X182" t="inlineStr">
         <is>
-          <t>01 (một) trái phiếu được nhận 6.158.082,192 đồng. - Ngày thanh toán: 29/06/2026 (Do ngày thanh toán không phải là ngày làm việc nên TCĐKCK sẽ thanh toán vào ngày làm việc ngay sau ngày đó) - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 6.158.082,192 đồng. - Ngày thanh toán: 29/06/2026 (Do ngày thanh toán không phải là ngày làm việc nên TCĐKCK sẽ thanh toán vào ngày làm việc ngay sau ngày đó)</t>
+          <t>29/06/2026 (Do ngày thanh toán không phải là ngày làm việc nên TCĐKCK sẽ thanh toán vào ngày làm việc ngay sau ngày đó) - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 6.158.082,192 đồng. - Ngày thanh toán: 29/06/2026 (Do ngày thanh toán không phải là ngày làm việc nên TCĐKCK sẽ thanh toán vào ngày làm việc ngay sau ngày đó) - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 6.158.082,192 đồng. - Ngày thanh toán: 29/06/2026 (Do ngày thanh toán không phải là ngày làm việc nên TCĐKCK sẽ thanh toán vào ngày làm việc ngay sau ngày đó)</t>
         </is>
       </c>
       <c r="Y182" t="n">
@@ -20411,14 +20355,10 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>01 (một) trái phiếu nhận được 2.898.630,137 đồng - Ngày thanh toán: 22/06/2026</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>22/06/2026 - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 2.898.630,137 đồng - Ngày thanh toán: 22/06/2026</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
@@ -20430,28 +20370,18 @@
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
+      <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr"/>
-      <c r="T183" t="n">
-        <v>92</v>
-      </c>
-      <c r="U183" t="n">
-        <v>365</v>
-      </c>
-      <c r="V183" t="n">
-        <v>0.03967391304347823</v>
-      </c>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
       <c r="W183" t="inlineStr"/>
       <c r="X183" t="inlineStr">
         <is>
-          <t>01 (một) trái phiếu nhận được 2.898.630,137 đồng - Ngày thanh toán: 22/06/2026 - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 2.898.630,137 đồng - Ngày thanh toán: 22/06/2026</t>
+          <t>22/06/2026 - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 2.898.630,137 đồng - Ngày thanh toán: 22/06/2026 - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 2.898.630,137 đồng - Ngày thanh toán: 22/06/2026</t>
         </is>
       </c>
       <c r="Y183" t="n">
@@ -20623,14 +20553,10 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 59.800.000 đồng - Ngày thanh toán: 29/6/2026</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 59.800.000 đồng - Ngày thanh toán: 29/6/2026</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
@@ -20642,28 +20568,18 @@
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
+      <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr"/>
-      <c r="T185" t="n">
-        <v>1</v>
-      </c>
-      <c r="U185" t="n">
-        <v>59800000</v>
-      </c>
-      <c r="V185" t="n">
-        <v>598000</v>
-      </c>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
       <c r="W185" t="inlineStr"/>
       <c r="X185" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 59.800.000 đồng - Ngày thanh toán: 29/6/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 59.800.000 đồng - Ngày thanh toán: 29/6/2026</t>
+          <t>29/6/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 59.800.000 đồng - Ngày thanh toán: 29/6/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 59.800.000 đồng - Ngày thanh toán: 29/6/2026</t>
         </is>
       </c>
       <c r="Y185" t="n">
@@ -20732,14 +20648,10 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>01 trái phiếu nhận được 59.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc).</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc). - Tỷ lệ thực hiện: 01 trái phiếu nhận được 59.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc).</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
@@ -20751,28 +20663,18 @@
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr"/>
-      <c r="T186" t="n">
-        <v>27</v>
-      </c>
-      <c r="U186" t="n">
-        <v>6</v>
-      </c>
-      <c r="V186" t="n">
-        <v>0.002222222222222222</v>
-      </c>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
       <c r="W186" t="inlineStr"/>
       <c r="X186" t="inlineStr">
         <is>
-          <t>01 trái phiếu nhận được 59.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc). - Tỷ lệ thực hiện: 01 trái phiếu nhận được 59.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc).</t>
+          <t>29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc). - Tỷ lệ thực hiện: 01 trái phiếu nhận được 59.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc). - Tỷ lệ thực hiện: 01 trái phiếu nhận được 59.300.000 đồng - Thời gian thực hiện: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc).</t>
         </is>
       </c>
       <c r="Y186" t="n">
@@ -20841,14 +20743,10 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>01 trái phiếu nhận được 69.000.000 đồng - Thời gian thực hiện: 29/6/2026</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 69.000.000 đồng - Thời gian thực hiện: 29/6/2026</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
@@ -20860,11 +20758,7 @@
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
+      <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr"/>
@@ -20875,7 +20769,7 @@
       <c r="W187" t="inlineStr"/>
       <c r="X187" t="inlineStr">
         <is>
-          <t>01 trái phiếu nhận được 69.000.000 đồng - Thời gian thực hiện: 29/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 69.000.000 đồng - Thời gian thực hiện: 29/6/2026</t>
+          <t>29/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 69.000.000 đồng - Thời gian thực hiện: 29/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 69.000.000 đồng - Thời gian thực hiện: 29/6/2026</t>
         </is>
       </c>
       <c r="Y187" t="n">
@@ -20950,7 +20844,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>100% - Thời gian đăng ký bán lại trái phiếu: Không có. Tổ chức phát hành sẽ thực hiện quyền mua lại trái phiếu vào ngày thực hiện quyền mua lại, người sở hữu trái phiếu có nghĩa vụ bán lại toàn bộ trái phiếu do mình sở hữu cho Tổ chức phát hành. Toàn bộ trái phiếu sau khi mua lại sẽ bị hủy đăng ký</t>
+          <t>Không có. Tổ chức phát hành sẽ thực hiện quyền mua lại trái phiếu vào ngày thực hiện quyền mua lại, người sở hữu trái phiếu có nghĩa vụ bán lại toàn bộ trái phiếu do mình sở hữu cho Tổ chức phát hành. Toàn bộ trái phiếu sau khi mua lại sẽ bị hủy đăng ký - Tỷ lệ thực hiện: 100% - Thời gian đăng ký bán lại trái phiếu: Không có. Tổ chức phát hành sẽ thực hiện quyền mua lại trái phiếu vào ngày thực hiện quyền mua lại, người sở hữu trái phiếu có nghĩa vụ bán lại toàn bộ trái phiếu do mình sở hữu cho Tổ chức phát hành. Toàn bộ trái phiếu sau khi mua lại sẽ bị hủy đăng ký</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -20986,7 +20880,7 @@
       <c r="W188" t="inlineStr"/>
       <c r="X188" t="inlineStr">
         <is>
-          <t>100% - Thời gian đăng ký bán lại trái phiếu: Không có. Tổ chức phát hành sẽ thực hiện quyền mua lại trái phiếu vào ngày thực hiện quyền mua lại, người sở hữu trái phiếu có nghĩa vụ bán lại toàn bộ trái phiếu do mình sở hữu cho Tổ chức phát hành. Toàn bộ trái phiếu sau khi mua lại sẽ bị hủy đăng ký - Tỷ lệ thực hiện: 100% - Thời gian đăng ký bán lại trái phiếu: Không có. Tổ chức phát hành sẽ thực hiện quyền mua lại trái phiếu vào ngày thực hiện quyền mua lại, người sở hữu trái phiếu có nghĩa vụ bán lại toàn bộ trái phiếu do mình sở hữu cho Tổ chức phát hành. Toàn bộ trái phiếu sau khi mua lại sẽ bị hủy đăng ký</t>
+          <t>Không có. Tổ chức phát hành sẽ thực hiện quyền mua lại trái phiếu vào ngày thực hiện quyền mua lại, người sở hữu trái phiếu có nghĩa vụ bán lại toàn bộ trái phiếu do mình sở hữu cho Tổ chức phát hành. Toàn bộ trái phiếu sau khi mua lại sẽ bị hủy đăng ký - Tỷ lệ thực hiện: 100% - Thời gian đăng ký bán lại trái phiếu: Không có. Tổ chức phát hành sẽ thực hiện quyền mua lại trái phiếu vào ngày thực hiện quyền mua lại, người sở hữu trái phiếu có nghĩa vụ bán lại toàn bộ trái phiếu do mình sở hữu cho Tổ chức phát hành. Toàn bộ trái phiếu sau khi mua lại sẽ bị hủy đăng ký - Tỷ lệ thực hiện: 100% - Thời gian đăng ký bán lại trái phiếu: Không có. Tổ chức phát hành sẽ thực hiện quyền mua lại trái phiếu vào ngày thực hiện quyền mua lại, người sở hữu trái phiếu có nghĩa vụ bán lại toàn bộ trái phiếu do mình sở hữu cho Tổ chức phát hành. Toàn bộ trái phiếu sau khi mua lại sẽ bị hủy đăng ký</t>
         </is>
       </c>
       <c r="Y188" t="n">
@@ -21059,7 +20953,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 25/6/2026</t>
+          <t>25/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 25/6/2026</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -21095,7 +20989,7 @@
       <c r="W189" t="inlineStr"/>
       <c r="X189" t="inlineStr">
         <is>
-          <t>Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 25/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 25/6/2026</t>
+          <t>25/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 25/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Ngày thanh toán tiền mua lại: 25/6/2026</t>
         </is>
       </c>
       <c r="Y189" t="n">
@@ -21168,7 +21062,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Thời gian thực hiện: 25/6/2026</t>
+          <t>25/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Thời gian thực hiện: 25/6/2026</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -21204,7 +21098,7 @@
       <c r="W190" t="inlineStr"/>
       <c r="X190" t="inlineStr">
         <is>
-          <t>Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Thời gian thực hiện: 25/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Thời gian thực hiện: 25/6/2026</t>
+          <t>25/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Thời gian thực hiện: 25/6/2026 - Tỷ lệ thực hiện: Mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành) - Thời gian thực hiện: 25/6/2026</t>
         </is>
       </c>
       <c r="Y190" t="n">
@@ -21275,14 +21169,10 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 60.892.877 đồng - Ngày thanh toán: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc)</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 60.892.877 đồng - Ngày thanh toán: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc)</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
@@ -21294,28 +21184,18 @@
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
-      <c r="T191" t="n">
-        <v>1</v>
-      </c>
-      <c r="U191" t="n">
-        <v>60892877</v>
-      </c>
-      <c r="V191" t="n">
-        <v>608928.77</v>
-      </c>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
       <c r="W191" t="inlineStr"/>
       <c r="X191" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 60.892.877 đồng - Ngày thanh toán: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 60.892.877 đồng - Ngày thanh toán: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc)</t>
+          <t>29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 60.892.877 đồng - Ngày thanh toán: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 60.892.877 đồng - Ngày thanh toán: 29/6/2026 (do ngày 27/6/2026 và 28/6/2026 không phải là ngày làm việc)</t>
         </is>
       </c>
       <c r="Y191" t="n">
@@ -21386,14 +21266,10 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 64.000.000 đồng - Ngày thanh toán: 30/6/2026</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 64.000.000 đồng - Ngày thanh toán: 30/6/2026</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
@@ -21405,28 +21281,18 @@
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+      <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
-      <c r="T192" t="n">
-        <v>1</v>
-      </c>
-      <c r="U192" t="n">
-        <v>64000000</v>
-      </c>
-      <c r="V192" t="n">
-        <v>640000</v>
-      </c>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr"/>
       <c r="W192" t="inlineStr"/>
       <c r="X192" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 64.000.000 đồng - Ngày thanh toán: 30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 64.000.000 đồng - Ngày thanh toán: 30/6/2026</t>
+          <t>30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 64.000.000 đồng - Ngày thanh toán: 30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 64.000.000 đồng - Ngày thanh toán: 30/6/2026</t>
         </is>
       </c>
       <c r="Y192" t="n">
@@ -21497,14 +21363,10 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 58.800.000 đồng - Ngày thanh toán: 30/6/2026</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.800.000 đồng - Ngày thanh toán: 30/6/2026</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
@@ -21516,28 +21378,18 @@
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+      <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
-      <c r="T193" t="n">
-        <v>1</v>
-      </c>
-      <c r="U193" t="n">
-        <v>58800000</v>
-      </c>
-      <c r="V193" t="n">
-        <v>588000</v>
-      </c>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
       <c r="W193" t="inlineStr"/>
       <c r="X193" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 58.800.000 đồng - Ngày thanh toán: 30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.800.000 đồng - Ngày thanh toán: 30/6/2026</t>
+          <t>30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.800.000 đồng - Ngày thanh toán: 30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.800.000 đồng - Ngày thanh toán: 30/6/2026</t>
         </is>
       </c>
       <c r="Y193" t="n">
@@ -21608,14 +21460,10 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 56.800.000 đồng - Ngày thanh toán: 29/6/2026 (Do ngày 27/6/2026 và ngày 28/6/2026 không phải là ngày làm việc)</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 (Do ngày 27/6/2026 và ngày 28/6/2026 không phải là ngày làm việc) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng - Ngày thanh toán: 29/6/2026 (Do ngày 27/6/2026 và ngày 28/6/2026 không phải là ngày làm việc)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
@@ -21627,28 +21475,18 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
-      <c r="T194" t="n">
-        <v>1</v>
-      </c>
-      <c r="U194" t="n">
-        <v>56800000</v>
-      </c>
-      <c r="V194" t="n">
-        <v>568000</v>
-      </c>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
       <c r="W194" t="inlineStr"/>
       <c r="X194" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 56.800.000 đồng - Ngày thanh toán: 29/6/2026 (Do ngày 27/6/2026 và ngày 28/6/2026 không phải là ngày làm việc) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng - Ngày thanh toán: 29/6/2026 (Do ngày 27/6/2026 và ngày 28/6/2026 không phải là ngày làm việc)</t>
+          <t>29/6/2026 (Do ngày 27/6/2026 và ngày 28/6/2026 không phải là ngày làm việc) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng - Ngày thanh toán: 29/6/2026 (Do ngày 27/6/2026 và ngày 28/6/2026 không phải là ngày làm việc) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng - Ngày thanh toán: 29/6/2026 (Do ngày 27/6/2026 và ngày 28/6/2026 không phải là ngày làm việc)</t>
         </is>
       </c>
       <c r="Y194" t="n">
@@ -22182,19 +22020,11 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>01 cổ phiếu - 01 quyền biểu quyết - Thời gian thực hiện: 8h30-12h00, Thứ Sáu ngày 31/07/2026</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu / Cổ phiếu thưởng</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu</t>
-        </is>
-      </c>
+          <t>8h30-12h00, Thứ Sáu ngày 31/07/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết - Thời gian thực hiện: 8h30-12h00, Thứ Sáu ngày 31/07/2026</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>VN000000HPT7</t>
@@ -22216,7 +22046,7 @@
       <c r="W201" t="inlineStr"/>
       <c r="X201" t="inlineStr">
         <is>
-          <t>01 cổ phiếu - 01 quyền biểu quyết - Thời gian thực hiện: 8h30-12h00, Thứ Sáu ngày 31/07/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết - Thời gian thực hiện: 8h30-12h00, Thứ Sáu ngày 31/07/2026</t>
+          <t>8h30-12h00, Thứ Sáu ngày 31/07/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết - Thời gian thực hiện: 8h30-12h00, Thứ Sáu ngày 31/07/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết - Thời gian thực hiện: 8h30-12h00, Thứ Sáu ngày 31/07/2026</t>
         </is>
       </c>
       <c r="Y201" t="n">
@@ -22446,19 +22276,11 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>10%/ cổ phiếu (1 cổ phiếu được nhận 1.000 đồng) - Ngày thanh toán: 19/06/2026</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu / Cổ phiếu thưởng</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu</t>
-        </is>
-      </c>
+          <t>19/06/2026 - Tỷ lệ thực hiện: 10%/ cổ phiếu (1 cổ phiếu được nhận 1.000 đồng) - Ngày thanh toán: 19/06/2026</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>VN000000SFI8</t>
@@ -22469,26 +22291,18 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
+      <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr"/>
-      <c r="T204" t="n">
-        <v>1</v>
-      </c>
-      <c r="U204" t="n">
-        <v>1000</v>
-      </c>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr"/>
       <c r="W204" t="inlineStr"/>
       <c r="X204" t="inlineStr">
         <is>
-          <t>10%/ cổ phiếu (1 cổ phiếu được nhận 1.000 đồng) - Ngày thanh toán: 19/06/2026 - Tỷ lệ thực hiện: 10%/ cổ phiếu (1 cổ phiếu được nhận 1.000 đồng) - Ngày thanh toán: 19/06/2026</t>
+          <t>19/06/2026 - Tỷ lệ thực hiện: 10%/ cổ phiếu (1 cổ phiếu được nhận 1.000 đồng) - Ngày thanh toán: 19/06/2026 - Tỷ lệ thực hiện: 10%/ cổ phiếu (1 cổ phiếu được nhận 1.000 đồng) - Ngày thanh toán: 19/06/2026</t>
         </is>
       </c>
       <c r="Y204" t="n">
@@ -22557,7 +22371,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>01(một) trái phiếu nhận được 3.989.041,0959 đồng. - Ngày thanh toán lãi: 22/06/2026</t>
+          <t>22/06/2026 - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 3.989.041,0959 đồng. - Ngày thanh toán lãi: 22/06/2026</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -22597,7 +22411,7 @@
       <c r="W205" t="inlineStr"/>
       <c r="X205" t="inlineStr">
         <is>
-          <t>01(một) trái phiếu nhận được 3.989.041,0959 đồng. - Ngày thanh toán lãi: 22/06/2026 - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 3.989.041,0959 đồng. - Ngày thanh toán lãi: 22/06/2026</t>
+          <t>22/06/2026 - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 3.989.041,0959 đồng. - Ngày thanh toán lãi: 22/06/2026 - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 3.989.041,0959 đồng. - Ngày thanh toán lãi: 22/06/2026</t>
         </is>
       </c>
       <c r="Y205" t="n">
@@ -23456,19 +23270,11 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>10%/cổ phiếu (1 cổ phiếu được nhận 1000 đồng) - Ngày thanh toán: 22/06/2026</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu / Cổ phiếu thưởng</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu</t>
-        </is>
-      </c>
+          <t>22/06/2026 - Tỷ lệ thực hiện: 10%/cổ phiếu (1 cổ phiếu được nhận 1000 đồng) - Ngày thanh toán: 22/06/2026</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>VN000000EVE4</t>
@@ -23479,26 +23285,18 @@
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
+      <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr"/>
-      <c r="T215" t="n">
-        <v>1</v>
-      </c>
-      <c r="U215" t="n">
-        <v>1000</v>
-      </c>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
       <c r="W215" t="inlineStr"/>
       <c r="X215" t="inlineStr">
         <is>
-          <t>10%/cổ phiếu (1 cổ phiếu được nhận 1000 đồng) - Ngày thanh toán: 22/06/2026 - Tỷ lệ thực hiện: 10%/cổ phiếu (1 cổ phiếu được nhận 1000 đồng) - Ngày thanh toán: 22/06/2026</t>
+          <t>22/06/2026 - Tỷ lệ thực hiện: 10%/cổ phiếu (1 cổ phiếu được nhận 1000 đồng) - Ngày thanh toán: 22/06/2026 - Tỷ lệ thực hiện: 10%/cổ phiếu (1 cổ phiếu được nhận 1000 đồng) - Ngày thanh toán: 22/06/2026</t>
         </is>
       </c>
       <c r="Y215" t="n">
@@ -23563,19 +23361,11 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>11%/cổ phiếu (1 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 05/08/2026</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu / Cổ phiếu thưởng</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu</t>
-        </is>
-      </c>
+          <t>05/08/2026 - Tỷ lệ thực hiện: 11%/cổ phiếu (1 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 05/08/2026</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>VN000000CDG1</t>
@@ -23586,26 +23376,18 @@
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
-        </is>
-      </c>
+      <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr"/>
-      <c r="T216" t="n">
-        <v>1</v>
-      </c>
-      <c r="U216" t="n">
-        <v>1100</v>
-      </c>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
       <c r="W216" t="inlineStr"/>
       <c r="X216" t="inlineStr">
         <is>
-          <t>11%/cổ phiếu (1 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 05/08/2026 - Tỷ lệ thực hiện: 11%/cổ phiếu (1 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 05/08/2026</t>
+          <t>05/08/2026 - Tỷ lệ thực hiện: 11%/cổ phiếu (1 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 05/08/2026 - Tỷ lệ thực hiện: 11%/cổ phiếu (1 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 05/08/2026</t>
         </is>
       </c>
       <c r="Y216" t="n">
@@ -23670,19 +23452,11 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>8,5%/cổ phiếu (1 cổ phiếu được nhận 850 đồng) - Ngày thanh toán: 20/07/2026</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu / Cổ phiếu thưởng</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu</t>
-        </is>
-      </c>
+          <t>20/07/2026 - Tỷ lệ thực hiện: 8,5%/cổ phiếu (1 cổ phiếu được nhận 850 đồng) - Ngày thanh toán: 20/07/2026</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>VN000000HNB0</t>
@@ -23693,26 +23467,18 @@
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
+      <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr"/>
-      <c r="T217" t="n">
-        <v>1</v>
-      </c>
-      <c r="U217" t="n">
-        <v>850</v>
-      </c>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
       <c r="W217" t="inlineStr"/>
       <c r="X217" t="inlineStr">
         <is>
-          <t>8,5%/cổ phiếu (1 cổ phiếu được nhận 850 đồng) - Ngày thanh toán: 20/07/2026 - Tỷ lệ thực hiện: 8,5%/cổ phiếu (1 cổ phiếu được nhận 850 đồng) - Ngày thanh toán: 20/07/2026</t>
+          <t>20/07/2026 - Tỷ lệ thực hiện: 8,5%/cổ phiếu (1 cổ phiếu được nhận 850 đồng) - Ngày thanh toán: 20/07/2026 - Tỷ lệ thực hiện: 8,5%/cổ phiếu (1 cổ phiếu được nhận 850 đồng) - Ngày thanh toán: 20/07/2026</t>
         </is>
       </c>
       <c r="Y217" t="n">
@@ -23777,7 +23543,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>14,512%/cổ phiếu (1 cổ phiếu được nhận 1.451,2 đồng). Trường hợp số tiền cổ tức phân chia bị lẻ thì được làm tròn đến hàng đơn vị đồng (nếu chữ số thập phân thứ nhất bằng hoặc lớn hơn 5 thì được làm tròn lên, nếu chữ số thập phân thứ nhất nhỏ hơn 5 thì phần thập phân bị hủy bỏ). - Ngày thanh toán: 22/06/2026</t>
+          <t>22/06/2026 - Tỷ lệ thực hiện: 14,512%/cổ phiếu (1 cổ phiếu được nhận 1.451,2 đồng). Trường hợp số tiền cổ tức phân chia bị lẻ thì được làm tròn đến hàng đơn vị đồng (nếu chữ số thập phân thứ nhất bằng hoặc lớn hơn 5 thì được làm tròn lên, nếu chữ số thập phân thứ nhất nhỏ hơn 5 thì phần thập phân bị hủy bỏ). - Ngày thanh toán: 22/06/2026</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -23819,7 +23585,7 @@
       <c r="W218" t="inlineStr"/>
       <c r="X218" t="inlineStr">
         <is>
-          <t>14,512%/cổ phiếu (1 cổ phiếu được nhận 1.451,2 đồng). Trường hợp số tiền cổ tức phân chia bị lẻ thì được làm tròn đến hàng đơn vị đồng (nếu chữ số thập phân thứ nhất bằng hoặc lớn hơn 5 thì được làm tròn lên, nếu chữ số thập phân thứ nhất nhỏ hơn 5 thì phần thập phân bị hủy bỏ). - Ngày thanh toán: 22/06/2026 - Tỷ lệ thực hiện: 14,512%/cổ phiếu (1 cổ phiếu được nhận 1.451,2 đồng). Trường hợp số tiền cổ tức phân chia bị lẻ thì được làm tròn đến hàng đơn vị đồng (nếu chữ số thập phân thứ nhất bằng hoặc lớn hơn 5 thì được làm tròn lên, nếu chữ số thập phân thứ nhất nhỏ hơn 5 thì phần thập phân bị hủy bỏ). - Ngày thanh toán: 22/06/2026</t>
+          <t>22/06/2026 - Tỷ lệ thực hiện: 14,512%/cổ phiếu (1 cổ phiếu được nhận 1.451,2 đồng). Trường hợp số tiền cổ tức phân chia bị lẻ thì được làm tròn đến hàng đơn vị đồng (nếu chữ số thập phân thứ nhất bằng hoặc lớn hơn 5 thì được làm tròn lên, nếu chữ số thập phân thứ nhất nhỏ hơn 5 thì phần thập phân bị hủy bỏ). - Ngày thanh toán: 22/06/2026 - Tỷ lệ thực hiện: 14,512%/cổ phiếu (1 cổ phiếu được nhận 1.451,2 đồng). Trường hợp số tiền cổ tức phân chia bị lẻ thì được làm tròn đến hàng đơn vị đồng (nếu chữ số thập phân thứ nhất bằng hoặc lớn hơn 5 thì được làm tròn lên, nếu chữ số thập phân thứ nhất nhỏ hơn 5 thì phần thập phân bị hủy bỏ). - Ngày thanh toán: 22/06/2026</t>
         </is>
       </c>
       <c r="Y218" t="n">
@@ -23887,14 +23653,10 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 07/7/2026</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>07/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 07/7/2026</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
@@ -23906,28 +23668,18 @@
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+      <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr"/>
-      <c r="T219" t="n">
-        <v>1</v>
-      </c>
-      <c r="U219" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="V219" t="n">
-        <v>6.375</v>
-      </c>
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr"/>
       <c r="W219" t="inlineStr"/>
       <c r="X219" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 07/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 07/7/2026</t>
+          <t>07/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 07/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 07/7/2026</t>
         </is>
       </c>
       <c r="Y219" t="n">
@@ -23996,14 +23748,10 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Từ và bao gồm ngày 24/3/2026 đến và không bao gồm ngày 24/6/2026, số ngày tính lãi 92 ngày - Tỷ lệ thực hiện: 01 trái phiếu được nhận 2.772.602,740 đồng. - Thời gian thực hiện: 24/6/2026</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>01 trái phiếu được nhận 2.772.602,740 đồng. - Thời gian thực hiện: 24/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 2.772.602,740 đồng. - Thời gian thực hiện: 24/6/2026</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
@@ -24015,28 +23763,18 @@
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
+      <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr"/>
-      <c r="T220" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U220" t="n">
-        <v>2772602740</v>
-      </c>
-      <c r="V220" t="n">
-        <v>27726.0274</v>
-      </c>
+      <c r="T220" t="inlineStr"/>
+      <c r="U220" t="inlineStr"/>
+      <c r="V220" t="inlineStr"/>
       <c r="W220" t="inlineStr"/>
       <c r="X220" t="inlineStr">
         <is>
-          <t>Từ và bao gồm ngày 24/3/2026 đến và không bao gồm ngày 24/6/2026, số ngày tính lãi 92 ngày - Tỷ lệ thực hiện: 01 trái phiếu được nhận 2.772.602,740 đồng. - Thời gian thực hiện: 24/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 2.772.602,740 đồng. - Thời gian thực hiện: 24/6/2026</t>
+          <t>01 trái phiếu được nhận 2.772.602,740 đồng. - Thời gian thực hiện: 24/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 2.772.602,740 đồng. - Thời gian thực hiện: 24/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 2.772.602,740 đồng. - Thời gian thực hiện: 24/6/2026</t>
         </is>
       </c>
       <c r="Y220" t="n">
@@ -24105,14 +23843,10 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>01 trái phiếu nhận được 1.613.150,68493 đồng - Thời gian thực hiện: 30/6/2026</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 1.613.150,68493 đồng - Thời gian thực hiện: 30/6/2026</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
@@ -24124,28 +23858,18 @@
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+      <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr"/>
-      <c r="T221" t="n">
-        <v>92</v>
-      </c>
-      <c r="U221" t="n">
-        <v>365</v>
-      </c>
-      <c r="V221" t="n">
-        <v>0.03967391304347823</v>
-      </c>
+      <c r="T221" t="inlineStr"/>
+      <c r="U221" t="inlineStr"/>
+      <c r="V221" t="inlineStr"/>
       <c r="W221" t="inlineStr"/>
       <c r="X221" t="inlineStr">
         <is>
-          <t>01 trái phiếu nhận được 1.613.150,68493 đồng - Thời gian thực hiện: 30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 1.613.150,68493 đồng - Thời gian thực hiện: 30/6/2026</t>
+          <t>30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 1.613.150,68493 đồng - Thời gian thực hiện: 30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 1.613.150,68493 đồng - Thời gian thực hiện: 30/6/2026</t>
         </is>
       </c>
       <c r="Y221" t="n">
@@ -24214,14 +23938,10 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ)</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ)</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
@@ -24233,28 +23953,18 @@
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
+      <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr"/>
-      <c r="T222" t="n">
-        <v>365</v>
-      </c>
-      <c r="U222" t="n">
-        <v>365</v>
-      </c>
-      <c r="V222" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr"/>
+      <c r="V222" t="inlineStr"/>
       <c r="W222" t="inlineStr"/>
       <c r="X222" t="inlineStr">
         <is>
-          <t>01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ)</t>
+          <t>20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ)</t>
         </is>
       </c>
       <c r="Y222" t="n">
@@ -24323,14 +24033,10 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 21/7/2026</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>21/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 21/7/2026</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
@@ -24342,28 +24048,18 @@
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>21/07/2026</t>
-        </is>
-      </c>
+      <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="inlineStr"/>
-      <c r="T223" t="n">
-        <v>365</v>
-      </c>
-      <c r="U223" t="n">
-        <v>365</v>
-      </c>
-      <c r="V223" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr"/>
       <c r="W223" t="inlineStr"/>
       <c r="X223" t="inlineStr">
         <is>
-          <t>01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 21/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 21/7/2026</t>
+          <t>21/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 21/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 6.375.000 đồng - Thời gian thực hiện: 21/7/2026</t>
         </is>
       </c>
       <c r="Y223" t="n">
@@ -24433,14 +24129,10 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
@@ -24452,28 +24144,18 @@
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
+      <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
       <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr"/>
-      <c r="T224" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U224" t="n">
-        <v>3362410959</v>
-      </c>
-      <c r="V224" t="n">
-        <v>33624.10959</v>
-      </c>
+      <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr"/>
       <c r="W224" t="inlineStr"/>
       <c r="X224" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
+          <t>29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
         </is>
       </c>
       <c r="Y224" t="n">
@@ -24543,14 +24225,10 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
@@ -24562,28 +24240,18 @@
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
+      <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr"/>
-      <c r="T225" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U225" t="n">
-        <v>3362410959</v>
-      </c>
-      <c r="V225" t="n">
-        <v>33624.10959</v>
-      </c>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr"/>
       <c r="W225" t="inlineStr"/>
       <c r="X225" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
+          <t>29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
         </is>
       </c>
       <c r="Y225" t="n">
@@ -24653,14 +24321,10 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
@@ -24672,28 +24336,18 @@
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
+      <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr"/>
-      <c r="T226" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U226" t="n">
-        <v>3362410959</v>
-      </c>
-      <c r="V226" t="n">
-        <v>33624.10959</v>
-      </c>
+      <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr"/>
       <c r="W226" t="inlineStr"/>
       <c r="X226" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
+          <t>29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó). - Tỷ lệ thực hiện: 1 trái phiếu được nhận 3.362.410,959 đồng. - Thời gian thực hiện: 29/6/2026 (do ngày thanh toán không phải là ngày làm việc nên tổ chức phát hành sẽ thanh toán vào ngày làm việc ngay sau ngày đó).</t>
         </is>
       </c>
       <c r="Y226" t="n">
@@ -24762,14 +24416,10 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 2.772.602,740 đồng - Thời gian thực hiện: 26/6/2026</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>26/6/2026 - Tỷ lệ thực hiện: 1 trái phiếu được nhận 2.772.602,740 đồng - Thời gian thực hiện: 26/6/2026</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
@@ -24781,28 +24431,18 @@
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
+      <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
       <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr"/>
-      <c r="T227" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U227" t="n">
-        <v>2772602740</v>
-      </c>
-      <c r="V227" t="n">
-        <v>27726.0274</v>
-      </c>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr"/>
       <c r="W227" t="inlineStr"/>
       <c r="X227" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 2.772.602,740 đồng - Thời gian thực hiện: 26/6/2026 - Tỷ lệ thực hiện: 1 trái phiếu được nhận 2.772.602,740 đồng - Thời gian thực hiện: 26/6/2026</t>
+          <t>26/6/2026 - Tỷ lệ thực hiện: 1 trái phiếu được nhận 2.772.602,740 đồng - Thời gian thực hiện: 26/6/2026 - Tỷ lệ thực hiện: 1 trái phiếu được nhận 2.772.602,740 đồng - Thời gian thực hiện: 26/6/2026</t>
         </is>
       </c>
       <c r="Y227" t="n">
@@ -24872,14 +24512,10 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 2.199.178,082 đồng - Ngày thanh toán: 29/6/2026</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 - Tỷ lệ thực hiện: 1 trái phiếu được nhận 2.199.178,082 đồng - Ngày thanh toán: 29/6/2026</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
@@ -24891,28 +24527,18 @@
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
+      <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
       <c r="Q228" t="inlineStr"/>
       <c r="R228" t="inlineStr"/>
       <c r="S228" t="inlineStr"/>
-      <c r="T228" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U228" t="n">
-        <v>2199178082</v>
-      </c>
-      <c r="V228" t="n">
-        <v>21991.78082</v>
-      </c>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr"/>
+      <c r="V228" t="inlineStr"/>
       <c r="W228" t="inlineStr"/>
       <c r="X228" t="inlineStr">
         <is>
-          <t>1 trái phiếu được nhận 2.199.178,082 đồng - Ngày thanh toán: 29/6/2026 - Tỷ lệ thực hiện: 1 trái phiếu được nhận 2.199.178,082 đồng - Ngày thanh toán: 29/6/2026</t>
+          <t>29/6/2026 - Tỷ lệ thực hiện: 1 trái phiếu được nhận 2.199.178,082 đồng - Ngày thanh toán: 29/6/2026 - Tỷ lệ thực hiện: 1 trái phiếu được nhận 2.199.178,082 đồng - Ngày thanh toán: 29/6/2026</t>
         </is>
       </c>
       <c r="Y228" t="n">
@@ -24985,11 +24611,7 @@
           <t>16/6/2026</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
@@ -25001,24 +24623,14 @@
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
+      <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr"/>
       <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr"/>
-      <c r="T229" t="n">
-        <v>182</v>
-      </c>
-      <c r="U229" t="n">
-        <v>365</v>
-      </c>
-      <c r="V229" t="n">
-        <v>0.02005494505494504</v>
-      </c>
+      <c r="T229" t="inlineStr"/>
+      <c r="U229" t="inlineStr"/>
+      <c r="V229" t="inlineStr"/>
       <c r="W229" t="inlineStr"/>
       <c r="X229" t="inlineStr">
         <is>
@@ -25090,14 +24702,10 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 7,025%/năm * 182 (ngày)/365 (ngày) = 3.502.876,71233 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 30/6/2026</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 7,025%/năm * 182 (ngày)/365 (ngày) = 3.502.876,71233 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 30/6/2026</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
@@ -25109,28 +24717,18 @@
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+      <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr"/>
       <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr"/>
-      <c r="T230" t="n">
-        <v>1</v>
-      </c>
-      <c r="U230" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="V230" t="n">
-        <v>7.025</v>
-      </c>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="inlineStr"/>
       <c r="W230" t="inlineStr"/>
       <c r="X230" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 7,025%/năm * 182 (ngày)/365 (ngày) = 3.502.876,71233 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 7,025%/năm * 182 (ngày)/365 (ngày) = 3.502.876,71233 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 30/6/2026</t>
+          <t>30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 7,025%/năm * 182 (ngày)/365 (ngày) = 3.502.876,71233 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 30/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 7,025%/năm * 182 (ngày)/365 (ngày) = 3.502.876,71233 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 30/6/2026</t>
         </is>
       </c>
       <c r="Y230" t="n">
@@ -25198,14 +24796,10 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 23/7/2026</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>23/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 23/7/2026</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
@@ -25217,28 +24811,18 @@
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
+      <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
-      <c r="T231" t="n">
-        <v>1</v>
-      </c>
-      <c r="U231" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="V231" t="n">
-        <v>6.475</v>
-      </c>
+      <c r="T231" t="inlineStr"/>
+      <c r="U231" t="inlineStr"/>
+      <c r="V231" t="inlineStr"/>
       <c r="W231" t="inlineStr"/>
       <c r="X231" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 23/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 23/7/2026</t>
+          <t>23/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 23/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 23/7/2026</t>
         </is>
       </c>
       <c r="Y231" t="n">
@@ -25307,14 +24891,10 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 4.986.301,370 đồng. - Ngày thanh toán: 25/6/2026</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>25/6/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.986.301,370 đồng. - Ngày thanh toán: 25/6/2026</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
@@ -25326,28 +24906,18 @@
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
-        </is>
-      </c>
+      <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
       <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr"/>
-      <c r="T232" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U232" t="n">
-        <v>4986301370</v>
-      </c>
-      <c r="V232" t="n">
-        <v>49863.0137</v>
-      </c>
+      <c r="T232" t="inlineStr"/>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="inlineStr"/>
       <c r="W232" t="inlineStr"/>
       <c r="X232" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 4.986.301,370 đồng. - Ngày thanh toán: 25/6/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.986.301,370 đồng. - Ngày thanh toán: 25/6/2026</t>
+          <t>25/6/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.986.301,370 đồng. - Ngày thanh toán: 25/6/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.986.301,370 đồng. - Ngày thanh toán: 25/6/2026</t>
         </is>
       </c>
       <c r="Y232" t="n">
@@ -25415,14 +24985,10 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,7%/năm * 92 (ngày)/365 (ngày) = 1.688.767,12329 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/6/2026</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>29/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,7%/năm * 92 (ngày)/365 (ngày) = 1.688.767,12329 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/6/2026</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
@@ -25434,28 +25000,18 @@
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
+      <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr"/>
-      <c r="T233" t="n">
-        <v>1</v>
-      </c>
-      <c r="U233" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="V233" t="n">
-        <v>6.7</v>
-      </c>
+      <c r="T233" t="inlineStr"/>
+      <c r="U233" t="inlineStr"/>
+      <c r="V233" t="inlineStr"/>
       <c r="W233" t="inlineStr"/>
       <c r="X233" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,7%/năm * 92 (ngày)/365 (ngày) = 1.688.767,12329 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,7%/năm * 92 (ngày)/365 (ngày) = 1.688.767,12329 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/6/2026</t>
+          <t>29/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,7%/năm * 92 (ngày)/365 (ngày) = 1.688.767,12329 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/6/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,7%/năm * 92 (ngày)/365 (ngày) = 1.688.767,12329 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/6/2026</t>
         </is>
       </c>
       <c r="Y233" t="n">
@@ -25523,14 +25079,10 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 16/7/2026</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>16/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 16/7/2026</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
@@ -25542,28 +25094,18 @@
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr">
-        <is>
-          <t>16/07/2026</t>
-        </is>
-      </c>
+      <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
       <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr"/>
-      <c r="T234" t="n">
-        <v>1</v>
-      </c>
-      <c r="U234" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="V234" t="n">
-        <v>6.475</v>
-      </c>
+      <c r="T234" t="inlineStr"/>
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="inlineStr"/>
       <c r="W234" t="inlineStr"/>
       <c r="X234" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 16/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 16/7/2026</t>
+          <t>16/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 16/7/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,475%/năm * 365 (ngày)/365 (ngày) = 6.475.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 16/7/2026</t>
         </is>
       </c>
       <c r="Y234" t="n">
@@ -25631,14 +25173,10 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ)</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Cổ tức tiền</t>
-        </is>
-      </c>
+          <t>20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ)</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
@@ -25650,28 +25188,18 @@
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
+      <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
       <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr"/>
-      <c r="T235" t="n">
-        <v>1</v>
-      </c>
-      <c r="U235" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="V235" t="n">
-        <v>6.375</v>
-      </c>
+      <c r="T235" t="inlineStr"/>
+      <c r="U235" t="inlineStr"/>
+      <c r="V235" t="inlineStr"/>
       <c r="W235" t="inlineStr"/>
       <c r="X235" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ)</t>
+          <t>20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ) - Tỷ lệ thực hiện: 01 trái phiếu được nhận 100.000.000 đồng * 6,375%/năm * 365 (ngày)/365 (ngày) = 6.375.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 20/7/2026 (do ngày 18/7/2026 và 19/7/2026 là ngày nghỉ)</t>
         </is>
       </c>
       <c r="Y235" t="n">
@@ -25738,19 +25266,11 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>11%/cổ phiếu (01 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 27/07/2026</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu / Cổ phiếu thưởng</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu</t>
-        </is>
-      </c>
+          <t>27/07/2026 - Tỷ lệ thực hiện: 11%/cổ phiếu (01 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 27/07/2026</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>VN000000BIO6</t>
@@ -25761,26 +25281,18 @@
       <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
+      <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr"/>
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr"/>
-      <c r="T236" t="n">
-        <v>1</v>
-      </c>
-      <c r="U236" t="n">
-        <v>1100</v>
-      </c>
+      <c r="T236" t="inlineStr"/>
+      <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
       <c r="W236" t="inlineStr"/>
       <c r="X236" t="inlineStr">
         <is>
-          <t>11%/cổ phiếu (01 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 27/07/2026 - Tỷ lệ thực hiện: 11%/cổ phiếu (01 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 27/07/2026</t>
+          <t>27/07/2026 - Tỷ lệ thực hiện: 11%/cổ phiếu (01 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 27/07/2026 - Tỷ lệ thực hiện: 11%/cổ phiếu (01 cổ phiếu được nhận 1.100 đồng) - Ngày thanh toán: 27/07/2026</t>
         </is>
       </c>
       <c r="Y236" t="n">
@@ -25847,19 +25359,11 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>20%/cổ phiếu (01 cổ phiếu được nhận 2.000 đồng), trong đó: - Ngày thanh toán: 19/06/2026</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu / Cổ phiếu thưởng</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu</t>
-        </is>
-      </c>
+          <t>- Ngày thanh toán: 19/06/2026 - Tỷ lệ thực hiện: 20%/cổ phiếu (01 cổ phiếu được nhận 2.000 đồng), trong đó: - Ngày thanh toán: 19/06/2026</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>VN000000PHN0</t>
@@ -25870,26 +25374,18 @@
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
+      <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
       <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr"/>
-      <c r="T237" t="n">
-        <v>1</v>
-      </c>
-      <c r="U237" t="n">
-        <v>2000</v>
-      </c>
+      <c r="T237" t="inlineStr"/>
+      <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr"/>
       <c r="W237" t="inlineStr"/>
       <c r="X237" t="inlineStr">
         <is>
-          <t>20%/cổ phiếu (01 cổ phiếu được nhận 2.000 đồng), trong đó: - Ngày thanh toán: 19/06/2026 - Tỷ lệ thực hiện: 20%/cổ phiếu (01 cổ phiếu được nhận 2.000 đồng), trong đó: - Ngày thanh toán: 19/06/2026</t>
+          <t>- Ngày thanh toán: 19/06/2026 - Tỷ lệ thực hiện: 20%/cổ phiếu (01 cổ phiếu được nhận 2.000 đồng), trong đó: - Ngày thanh toán: 19/06/2026 - Tỷ lệ thực hiện: 20%/cổ phiếu (01 cổ phiếu được nhận 2.000 đồng), trong đó: - Ngày thanh toán: 19/06/2026</t>
         </is>
       </c>
       <c r="Y237" t="n">
@@ -26060,16 +25556,8 @@
           <t>20%/cổ phiếu (Người sở hữu 10 cổ phiếu được nhận 02 cổ phiếu mới)</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu / Cổ phiếu thưởng</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Cổ tức cổ phiếu</t>
-        </is>
-      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>VN000000NTP5</t>
@@ -26085,12 +25573,8 @@
       <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
-      <c r="T239" t="n">
-        <v>10</v>
-      </c>
-      <c r="U239" t="n">
-        <v>2</v>
-      </c>
+      <c r="T239" t="inlineStr"/>
+      <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
       <c r="W239" t="inlineStr"/>
       <c r="X239" t="inlineStr">
@@ -26220,7 +25704,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>15/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026</t>
+          <t>01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026</t>
         </is>
       </c>
       <c r="G241" t="inlineStr"/>
@@ -26246,7 +25730,7 @@
       <c r="W241" t="inlineStr"/>
       <c r="X241" t="inlineStr">
         <is>
-          <t>15/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026</t>
+          <t>01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 4.658.904,110 đồng. - Thời gian thực hiện: 15/5/2026</t>
         </is>
       </c>
       <c r="Y241" t="n">
@@ -26421,7 +25905,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026.</t>
+          <t>1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026.</t>
         </is>
       </c>
       <c r="G243" t="inlineStr"/>
@@ -26447,7 +25931,7 @@
       <c r="W243" t="inlineStr"/>
       <c r="X243" t="inlineStr">
         <is>
-          <t>09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026.</t>
+          <t>1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026.</t>
         </is>
       </c>
       <c r="Y243" t="n">
@@ -26520,7 +26004,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026.</t>
+          <t>1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026.</t>
         </is>
       </c>
       <c r="G244" t="inlineStr"/>
@@ -26546,7 +26030,7 @@
       <c r="W244" t="inlineStr"/>
       <c r="X244" t="inlineStr">
         <is>
-          <t>09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026.</t>
+          <t>1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026. - Tỷ lệ thực hiện: 1,8%/cổ phiếu (01 cổ phiếu được nhận 180 đồng). - Ngày thanh toán: 09/06/2026.</t>
         </is>
       </c>
       <c r="Y244" t="n">
@@ -26615,7 +26099,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>19/5/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026</t>
+          <t>01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026</t>
         </is>
       </c>
       <c r="G245" t="inlineStr"/>
@@ -26641,7 +26125,7 @@
       <c r="W245" t="inlineStr"/>
       <c r="X245" t="inlineStr">
         <is>
-          <t>19/5/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026</t>
+          <t>01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 4.958.904 đồng. - Ngày thanh toán:                  19/5/2026</t>
         </is>
       </c>
       <c r="Y245" t="n">
@@ -26715,7 +26199,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới).</t>
+          <t>4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới).</t>
         </is>
       </c>
       <c r="G246" t="inlineStr"/>
@@ -26741,7 +26225,7 @@
       <c r="W246" t="inlineStr"/>
       <c r="X246" t="inlineStr">
         <is>
-          <t>1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới).</t>
+          <t>4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới).</t>
         </is>
       </c>
       <c r="Y246" t="n">
@@ -26815,7 +26299,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới).</t>
+          <t>4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới).</t>
         </is>
       </c>
       <c r="G247" t="inlineStr"/>
@@ -26841,7 +26325,7 @@
       <c r="W247" t="inlineStr"/>
       <c r="X247" t="inlineStr">
         <is>
-          <t>1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới).</t>
+          <t>4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới). - Tỷ lệ thực hiện: 4:1 (Người sở hữu 04 cổ phiếu được nhận 01 cổ phiếu mới).</t>
         </is>
       </c>
       <c r="Y247" t="n">
@@ -26912,7 +26396,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026</t>
+          <t>01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026</t>
         </is>
       </c>
       <c r="G248" t="inlineStr"/>
@@ -26938,7 +26422,7 @@
       <c r="W248" t="inlineStr"/>
       <c r="X248" t="inlineStr">
         <is>
-          <t>20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026</t>
+          <t>01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 56.800.000 đồng. - Ngày thanh toán: 20/5/2026</t>
         </is>
       </c>
       <c r="Y248" t="n">
@@ -27010,7 +26494,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 22/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 22/05/2026.</t>
+          <t>22/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 22/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 22/05/2026.</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -27044,7 +26528,7 @@
       <c r="W249" t="inlineStr"/>
       <c r="X249" t="inlineStr">
         <is>
-          <t>Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 22/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 22/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 22/05/2026.</t>
+          <t>22/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 22/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 22/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 22/05/2026.</t>
         </is>
       </c>
       <c r="Y249" t="n">
@@ -27115,7 +26599,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>20/5/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026.</t>
+          <t>01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026.</t>
         </is>
       </c>
       <c r="G250" t="inlineStr"/>
@@ -27141,7 +26625,7 @@
       <c r="W250" t="inlineStr"/>
       <c r="X250" t="inlineStr">
         <is>
-          <t>20/5/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026.</t>
+          <t>01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 58.300.000 đồng. - Ngày thanh toán: 20/5/2026.</t>
         </is>
       </c>
       <c r="Y250" t="n">
@@ -27213,7 +26697,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 21/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 21/05/2026.</t>
+          <t>21/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 21/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 21/05/2026.</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -27247,7 +26731,7 @@
       <c r="W251" t="inlineStr"/>
       <c r="X251" t="inlineStr">
         <is>
-          <t>Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 21/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 21/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 21/05/2026.</t>
+          <t>21/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 21/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 21/05/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 21/05/2026.</t>
         </is>
       </c>
       <c r="Y251" t="n">
@@ -27316,7 +26800,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026</t>
+          <t>01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026</t>
         </is>
       </c>
       <c r="G252" t="inlineStr"/>
@@ -27342,7 +26826,7 @@
       <c r="W252" t="inlineStr"/>
       <c r="X252" t="inlineStr">
         <is>
-          <t>20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026</t>
+          <t>01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 31.042.740 đồng. - Thời gian thực hiện:20/5/2026</t>
         </is>
       </c>
       <c r="Y252" t="n">
@@ -27412,7 +26896,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>27/5/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026.</t>
+          <t>Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026.</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -27446,7 +26930,7 @@
       <c r="W253" t="inlineStr"/>
       <c r="X253" t="inlineStr">
         <is>
-          <t>27/5/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026.</t>
+          <t>Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026. - Tỷ lệ thực hiện: Mua lại trước hạn toàn bộ số lượng trái phiếu của người sở hữu trái phiếu. - Ngày thanh toán tiền mua lại: 27/5/2026.</t>
         </is>
       </c>
       <c r="Y253" t="n">
@@ -27613,7 +27097,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>20/05/2026. - Tỷ lệ thực hiện: 40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026. - Tỷ lệ thực hiện: 40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026.</t>
+          <t>40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026. - Tỷ lệ thực hiện: 40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026. - Tỷ lệ thực hiện: 40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026.</t>
         </is>
       </c>
       <c r="G255" t="inlineStr"/>
@@ -27639,7 +27123,7 @@
       <c r="W255" t="inlineStr"/>
       <c r="X255" t="inlineStr">
         <is>
-          <t>20/05/2026. - Tỷ lệ thực hiện: 40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026. - Tỷ lệ thực hiện: 40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026. - Tỷ lệ thực hiện: 40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026.</t>
+          <t>40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026. - Tỷ lệ thực hiện: 40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026. - Tỷ lệ thực hiện: 40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026. - Tỷ lệ thực hiện: 40%/ cổ phiếu (1 cổ phiếu được nhận 4.000 đồng). - Ngày thanh toán: 20/05/2026.</t>
         </is>
       </c>
       <c r="Y255" t="n">
@@ -27708,7 +27192,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>21/05/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026.</t>
+          <t>01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026.</t>
         </is>
       </c>
       <c r="G256" t="inlineStr"/>
@@ -27734,7 +27218,7 @@
       <c r="W256" t="inlineStr"/>
       <c r="X256" t="inlineStr">
         <is>
-          <t>21/05/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026.</t>
+          <t>01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026.</t>
         </is>
       </c>
       <c r="Y256" t="n">
@@ -27803,7 +27287,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>21/05/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026.</t>
+          <t>01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026.</t>
         </is>
       </c>
       <c r="G257" t="inlineStr"/>
@@ -27829,7 +27313,7 @@
       <c r="W257" t="inlineStr"/>
       <c r="X257" t="inlineStr">
         <is>
-          <t>21/05/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026.</t>
+          <t>01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 6.248.219,178 VNĐ. - Ngày thanh toán: 21/05/2026.</t>
         </is>
       </c>
       <c r="Y257" t="n">
@@ -27904,7 +27388,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>15/5/2026 - Tỷ lệ thực hiện: 100%. - Ngày thanh toán tiền mua lại: 15/5/2026 - Tỷ lệ thực hiện: 100%. - Ngày thanh toán tiền mua lại: 15/5/2026</t>
+          <t>100%. - Ngày thanh toán tiền mua lại: 15/5/2026 - Tỷ lệ thực hiện: 100%. - Ngày thanh toán tiền mua lại: 15/5/2026 - Tỷ lệ thực hiện: 100%. - Ngày thanh toán tiền mua lại: 15/5/2026</t>
         </is>
       </c>
       <c r="G258" t="inlineStr"/>
@@ -27930,7 +27414,7 @@
       <c r="W258" t="inlineStr"/>
       <c r="X258" t="inlineStr">
         <is>
-          <t>15/5/2026 - Tỷ lệ thực hiện: 100%. - Ngày thanh toán tiền mua lại: 15/5/2026 - Tỷ lệ thực hiện: 100%. - Ngày thanh toán tiền mua lại: 15/5/2026 - Tỷ lệ thực hiện: 100%. - Ngày thanh toán tiền mua lại: 15/5/2026</t>
+          <t>100%. - Ngày thanh toán tiền mua lại: 15/5/2026 - Tỷ lệ thực hiện: 100%. - Ngày thanh toán tiền mua lại: 15/5/2026 - Tỷ lệ thực hiện: 100%. - Ngày thanh toán tiền mua lại: 15/5/2026 - Tỷ lệ thực hiện: 100%. - Ngày thanh toán tiền mua lại: 15/5/2026</t>
         </is>
       </c>
       <c r="Y258" t="n">
@@ -27999,7 +27483,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>20/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026.</t>
+          <t>01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026.</t>
         </is>
       </c>
       <c r="G259" t="inlineStr"/>
@@ -28025,7 +27509,7 @@
       <c r="W259" t="inlineStr"/>
       <c r="X259" t="inlineStr">
         <is>
-          <t>20/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026.</t>
+          <t>01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.653.205,479 đồng. - Thời gian thực hiện: 20/5/2026.</t>
         </is>
       </c>
       <c r="Y259" t="n">
@@ -28405,7 +27889,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>13/5/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026</t>
+          <t>01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026</t>
         </is>
       </c>
       <c r="G263" t="inlineStr"/>
@@ -28431,7 +27915,7 @@
       <c r="W263" t="inlineStr"/>
       <c r="X263" t="inlineStr">
         <is>
-          <t>13/5/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026</t>
+          <t>01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026 - Tỷ lệ thực hiện:01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện:13/5/2026</t>
         </is>
       </c>
       <c r="Y263" t="n">
@@ -28600,7 +28084,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>11/06/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026</t>
+          <t>01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026</t>
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
@@ -28626,7 +28110,7 @@
       <c r="W265" t="inlineStr"/>
       <c r="X265" t="inlineStr">
         <is>
-          <t>11/06/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026</t>
+          <t>01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026 - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: 11/06/2026</t>
         </is>
       </c>
       <c r="Y265" t="n">
@@ -28690,7 +28174,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>12/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026.</t>
+          <t>01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026.</t>
         </is>
       </c>
       <c r="G266" t="inlineStr"/>
@@ -28720,7 +28204,7 @@
       <c r="W266" t="inlineStr"/>
       <c r="X266" t="inlineStr">
         <is>
-          <t>12/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026.</t>
+          <t>01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026. - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.500 đồng - Ngày thanh toán: 12/5/2026.</t>
         </is>
       </c>
       <c r="Y266" t="n">
@@ -28887,7 +28371,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>15/5/2026. - Tỷ lệ thực hiện:  01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026. - Tỷ lệ thực hiện:  01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026.</t>
+          <t>01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026. - Tỷ lệ thực hiện:  01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026. - Tỷ lệ thực hiện:  01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026.</t>
         </is>
       </c>
       <c r="G268" t="inlineStr"/>
@@ -28913,7 +28397,7 @@
       <c r="W268" t="inlineStr"/>
       <c r="X268" t="inlineStr">
         <is>
-          <t>15/5/2026. - Tỷ lệ thực hiện:  01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026. - Tỷ lệ thực hiện:  01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026. - Tỷ lệ thực hiện:  01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026.</t>
+          <t>01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026. - Tỷ lệ thực hiện:  01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026. - Tỷ lệ thực hiện:  01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026. - Tỷ lệ thực hiện:  01 trái phiếu được nhận 3.047.945,205 đồng. - Ngày thanh toán: 15/5/2026.</t>
         </is>
       </c>
       <c r="Y268" t="n">
@@ -29000,11 +28484,19 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tin chứng khoán</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
+          <t>855.113/10.000 (Trái Phiếu sẽ được chào bán cho cổ đông sở hữu cổ phần phổ thông của Tổ chức đăng ký chứng khoán theo tỷ lệ cứ mỗi cổ phần phổ thông mà cổ đông đó sở hữu vào ngày chốt danh sách cổ đông thì cổ đông đó sẽ có 01 (một) quyền mua, và cổ đông sở hữu 85,5113 (Tám mươi lăm phẩy năm một một ba) quyền mua sẽ được mua 1 (một) Trái Phiếu); và quyền mua được chuyển nhượng 01 (một) lần. - Giá phát hành: 100.000 đồng/trái phiếu</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Đăng ký Lưu ký</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Đăng ký</t>
+        </is>
+      </c>
       <c r="I269" t="inlineStr">
         <is>
           <t>VN000000SBT4</t>
@@ -29024,24 +28516,24 @@
       <c r="Q269" t="inlineStr"/>
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr"/>
-      <c r="T269" t="inlineStr"/>
-      <c r="U269" t="inlineStr"/>
+      <c r="T269" t="n">
+        <v>113</v>
+      </c>
+      <c r="U269" t="n">
+        <v>10000</v>
+      </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" t="inlineStr">
         <is>
           <t>100.000</t>
         </is>
       </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>Tin chứng khoán - Tỷ lệ thực hiện: 855.113/10.000 (Trái Phiếu sẽ được chào bán cho cổ đông sở hữu cổ phần phổ thông của Tổ chức đăng ký chứng khoán theo tỷ lệ cứ mỗi cổ phần phổ thông mà cổ đông đó sở hữu vào ngày chốt danh sách cổ đông thì cổ đông đó sẽ có 01 (một) quyền mua, và cổ đông sở hữu 85,5113 (Tám mươi lăm phẩy năm một một ba) quyền mua sẽ được mua 1 (một) Trái Phiếu); và quyền mua được chuyển nhượng 01 (một) lần. - Giá phát hành: 100.000 đồng/trái phiếu</t>
-        </is>
-      </c>
+      <c r="X269" t="inlineStr"/>
       <c r="Y269" t="n">
         <v>0</v>
       </c>
       <c r="Z269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -29904,7 +29396,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>22/04/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026</t>
+          <t>01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026</t>
         </is>
       </c>
       <c r="G278" t="inlineStr"/>
@@ -29930,7 +29422,7 @@
       <c r="W278" t="inlineStr"/>
       <c r="X278" t="inlineStr">
         <is>
-          <t>22/04/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026</t>
+          <t>01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 2.681.506,849 đồng. - Ngày thanh toán: 22/04/2026</t>
         </is>
       </c>
       <c r="Y278" t="n">
@@ -30003,7 +29495,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>22/4/2026. - Tỷ lệ thực hiện: mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026. - Tỷ lệ thực hiện: mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026.</t>
+          <t>mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026. - Tỷ lệ thực hiện: mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026. - Tỷ lệ thực hiện: mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026.</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -30039,7 +29531,7 @@
       <c r="W279" t="inlineStr"/>
       <c r="X279" t="inlineStr">
         <is>
-          <t>22/4/2026. - Tỷ lệ thực hiện: mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026. - Tỷ lệ thực hiện: mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026. - Tỷ lệ thực hiện: mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026.</t>
+          <t>mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026. - Tỷ lệ thực hiện: mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026. - Tỷ lệ thực hiện: mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026. - Tỷ lệ thực hiện: mua lại toàn bộ số lượng trái phiếu của người sở hữu trái phiếu (mua lại 100% trái phiếu đang lưu hành). - Ngày thanh toán tiền mua lại: 22/4/2026.</t>
         </is>
       </c>
       <c r="Y279" t="n">
@@ -30206,7 +29698,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026</t>
+          <t>21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026</t>
         </is>
       </c>
       <c r="G281" t="inlineStr"/>
@@ -30232,7 +29724,7 @@
       <c r="W281" t="inlineStr"/>
       <c r="X281" t="inlineStr">
         <is>
-          <t>01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026</t>
+          <t>21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026 - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.235.616,438 đồng - Thời gian thực hiện: 21/4/2026</t>
         </is>
       </c>
       <c r="Y281" t="n">
@@ -30300,7 +29792,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>29/4/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026</t>
+          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026</t>
         </is>
       </c>
       <c r="G282" t="inlineStr"/>
@@ -30326,7 +29818,7 @@
       <c r="W282" t="inlineStr"/>
       <c r="X282" t="inlineStr">
         <is>
-          <t>29/4/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026</t>
+          <t>01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 100.000.000 đồng * 6,275%/năm * 365 (ngày)/365 (ngày) = 6.275.000 đồng, làm tròn đến chữ số thập phân thứ 5 sau dấu phẩy. - Ngày thanh toán: 29/4/2026</t>
         </is>
       </c>
       <c r="Y282" t="n">
@@ -30862,7 +30354,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>15/4/2026 - Tỷ lệ thực hiện: mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026 - Tỷ lệ thực hiện: mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026</t>
+          <t>mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026 - Tỷ lệ thực hiện: mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026 - Tỷ lệ thực hiện: mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -30898,7 +30390,7 @@
       <c r="W288" t="inlineStr"/>
       <c r="X288" t="inlineStr">
         <is>
-          <t>15/4/2026 - Tỷ lệ thực hiện: mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026 - Tỷ lệ thực hiện: mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026 - Tỷ lệ thực hiện: mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026</t>
+          <t>mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026 - Tỷ lệ thực hiện: mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026 - Tỷ lệ thực hiện: mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026 - Tỷ lệ thực hiện: mua lại 100% số lượng trái phiếu của người sở hữu trái phiếu - Ngày thanh toán tiền mua lại: 15/4/2026</t>
         </is>
       </c>
       <c r="Y288" t="n">
@@ -31159,7 +30651,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>01/04/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026.</t>
+          <t>01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026.</t>
         </is>
       </c>
       <c r="G291" t="inlineStr"/>
@@ -31185,7 +30677,7 @@
       <c r="W291" t="inlineStr"/>
       <c r="X291" t="inlineStr">
         <is>
-          <t>01/04/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026.</t>
+          <t>01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 5.484.931,507 đồng. - Thời gian thực hiện: 01/04/2026.</t>
         </is>
       </c>
       <c r="Y291" t="n">
@@ -31250,7 +30742,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026</t>
+          <t>01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026</t>
         </is>
       </c>
       <c r="G292" t="inlineStr"/>
@@ -31280,7 +30772,7 @@
       <c r="W292" t="inlineStr"/>
       <c r="X292" t="inlineStr">
         <is>
-          <t>11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026</t>
+          <t>01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 1.500 đồng - Ngày thanh toán: 11/4/2026</t>
         </is>
       </c>
       <c r="Y292" t="n">
@@ -31345,7 +30837,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026</t>
+          <t>01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026</t>
         </is>
       </c>
       <c r="G293" t="inlineStr"/>
@@ -31375,7 +30867,7 @@
       <c r="W293" t="inlineStr"/>
       <c r="X293" t="inlineStr">
         <is>
-          <t>11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026</t>
+          <t>01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 2.400 đồng - Ngày thanh toán: 11/4/2026</t>
         </is>
       </c>
       <c r="Y293" t="n">
@@ -31439,7 +30931,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>13/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026</t>
+          <t>01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026</t>
         </is>
       </c>
       <c r="G294" t="inlineStr"/>
@@ -31469,7 +30961,7 @@
       <c r="W294" t="inlineStr"/>
       <c r="X294" t="inlineStr">
         <is>
-          <t>13/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026</t>
+          <t>01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026 - Tỷ lệ thanh toán: 01 trái phiếu được nhận 3.200 đồng - Ngày thanh toán: 13/4/2026</t>
         </is>
       </c>
       <c r="Y294" t="n">
@@ -31859,7 +31351,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>26/03/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026.</t>
+          <t>01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026.</t>
         </is>
       </c>
       <c r="G298" t="inlineStr"/>
@@ -31885,7 +31377,7 @@
       <c r="W298" t="inlineStr"/>
       <c r="X298" t="inlineStr">
         <is>
-          <t>26/03/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026.</t>
+          <t>01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026. - Tỷ lệ thực hiện: 01 trái phiếu được nhận 109.170 đồng. - Thời gian thực hiện: 26/03/2026.</t>
         </is>
       </c>
       <c r="Y298" t="n">
@@ -32058,7 +31550,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>03/04/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026.</t>
+          <t>01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026.</t>
         </is>
       </c>
       <c r="G300" t="inlineStr"/>
@@ -32084,7 +31576,7 @@
       <c r="W300" t="inlineStr"/>
       <c r="X300" t="inlineStr">
         <is>
-          <t>03/04/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026.</t>
+          <t>01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026. - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 2.712.328,767 VNĐ. - Ngày thanh toán: 03/04/2026.</t>
         </is>
       </c>
       <c r="Y300" t="n">
@@ -32363,11 +31855,19 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Tin chứng khoán</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr"/>
+          <t>01 (một) trái phiếu được nhận 6.372.191,781 VNĐ. - Ngày thanh toán: 30/03/2026 (Do ngày thanh toán không phải là ngày làm việc nên tổ chức đăng ký chứng khoán sẽ thanh toán vào ngày làm việc ngay sau đó).</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Đăng ký Lưu ký</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Đăng ký</t>
+        </is>
+      </c>
       <c r="I303" t="inlineStr">
         <is>
           <t>VN0SGJ123014</t>
@@ -32378,25 +31878,29 @@
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
       <c r="N303" t="inlineStr"/>
-      <c r="O303" t="inlineStr"/>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
       <c r="P303" t="inlineStr"/>
       <c r="Q303" t="inlineStr"/>
       <c r="R303" t="inlineStr"/>
       <c r="S303" t="inlineStr"/>
-      <c r="T303" t="inlineStr"/>
-      <c r="U303" t="inlineStr"/>
+      <c r="T303" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U303" t="n">
+        <v>6372191781</v>
+      </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" t="inlineStr"/>
-      <c r="X303" t="inlineStr">
-        <is>
-          <t>Tin chứng khoán - Tỷ lệ thực hiện: 01 (một) trái phiếu được nhận 6.372.191,781 VNĐ. - Ngày thanh toán: 30/03/2026 (Do ngày thanh toán không phải là ngày làm việc nên tổ chức đăng ký chứng khoán sẽ thanh toán vào ngày làm việc ngay sau đó).</t>
-        </is>
-      </c>
+      <c r="X303" t="inlineStr"/>
       <c r="Y303" t="n">
         <v>0</v>
       </c>
       <c r="Z303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
@@ -33214,7 +32718,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Ngày 17/04/2026. - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026. - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026.</t>
+          <t>01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026. - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026. - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026.</t>
         </is>
       </c>
       <c r="G311" t="inlineStr"/>
@@ -33240,7 +32744,7 @@
       <c r="W311" t="inlineStr"/>
       <c r="X311" t="inlineStr">
         <is>
-          <t>Ngày 17/04/2026. - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026. - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026. - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026.</t>
+          <t>01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026. - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026. - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026. - Tỷ lệ thực hiện: 01 cổ phiếu - 01 quyền biểu quyết. - Thời gian thực hiện: Ngày 17/04/2026.</t>
         </is>
       </c>
       <c r="Y311" t="n">
@@ -34353,7 +33857,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>17/04/2026 - Tỷ lệ thực hiện: 15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026 - Tỷ lệ thực hiện: 15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026</t>
+          <t>15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026 - Tỷ lệ thực hiện: 15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026 - Tỷ lệ thực hiện: 15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026</t>
         </is>
       </c>
       <c r="G322" t="inlineStr"/>
@@ -34379,7 +33883,7 @@
       <c r="W322" t="inlineStr"/>
       <c r="X322" t="inlineStr">
         <is>
-          <t>17/04/2026 - Tỷ lệ thực hiện: 15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026 - Tỷ lệ thực hiện: 15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026 - Tỷ lệ thực hiện: 15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026</t>
+          <t>15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026 - Tỷ lệ thực hiện: 15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026 - Tỷ lệ thực hiện: 15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026 - Tỷ lệ thực hiện: 15%/cổ phiếu (01 cổ phiếu được nhận 1.500 đồng). - Thời gian thực hiện: 17/04/2026</t>
         </is>
       </c>
       <c r="Y322" t="n">
@@ -34648,7 +34152,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>26/03/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026.</t>
+          <t>01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026.</t>
         </is>
       </c>
       <c r="G325" t="inlineStr"/>
@@ -34674,7 +34178,7 @@
       <c r="W325" t="inlineStr"/>
       <c r="X325" t="inlineStr">
         <is>
-          <t>26/03/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026.</t>
+          <t>01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026. - Tỷ lệ thực hiện: 01(một) trái phiếu nhận được 2.406.575,342 VNĐ. - Ngày thanh toán: 26/03/2026.</t>
         </is>
       </c>
       <c r="Y325" t="n">
@@ -35666,7 +35170,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>15/01/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026</t>
+          <t>01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026</t>
         </is>
       </c>
       <c r="G335" t="inlineStr"/>
@@ -35692,7 +35196,7 @@
       <c r="W335" t="inlineStr"/>
       <c r="X335" t="inlineStr">
         <is>
-          <t>15/01/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026</t>
+          <t>01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026 - Tỷ lệ thực hiện:  01 trái phiếu được nhận 24.583.333,333 đồng - Ngày thanh toán:                  15/01/2026</t>
         </is>
       </c>
       <c r="Y335" t="n">
@@ -35756,7 +35260,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>20/01/2026 - Tỷ lệ thực hiện: 5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026 - Tỷ lệ thực hiện: 5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026</t>
+          <t>5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026 - Tỷ lệ thực hiện: 5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026 - Tỷ lệ thực hiện: 5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026</t>
         </is>
       </c>
       <c r="G336" t="inlineStr"/>
@@ -35782,7 +35286,7 @@
       <c r="W336" t="inlineStr"/>
       <c r="X336" t="inlineStr">
         <is>
-          <t>20/01/2026 - Tỷ lệ thực hiện: 5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026 - Tỷ lệ thực hiện: 5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026 - Tỷ lệ thực hiện: 5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026</t>
+          <t>5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026 - Tỷ lệ thực hiện: 5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026 - Tỷ lệ thực hiện: 5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026 - Tỷ lệ thực hiện: 5%/ cổ phiếu (01 cổ phiếu được nhận 500 đồng). - Ngày thanh toán: 20/01/2026</t>
         </is>
       </c>
       <c r="Y336" t="n">
@@ -36068,7 +35572,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật)</t>
+          <t>01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật)</t>
         </is>
       </c>
       <c r="G339" t="inlineStr"/>
@@ -36094,7 +35598,7 @@
       <c r="W339" t="inlineStr"/>
       <c r="X339" t="inlineStr">
         <is>
-          <t>26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật)</t>
+          <t>01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật)</t>
         </is>
       </c>
       <c r="Y339" t="n">
@@ -36174,7 +35678,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật)</t>
+          <t>26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật)</t>
         </is>
       </c>
       <c r="G340" t="inlineStr"/>
@@ -36200,7 +35704,7 @@
       <c r="W340" t="inlineStr"/>
       <c r="X340" t="inlineStr">
         <is>
-          <t>01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật)</t>
+          <t>26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật) - Tỷ lệ thực hiện: 01 (một) trái phiếu nhận được 1.802,192 đồng. - Ngày thanh toán: 26/01/2026 (do ngày 25/01/2026 là Chủ nhật)</t>
         </is>
       </c>
       <c r="Y340" t="n">
@@ -36270,7 +35774,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>26/01/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026</t>
+          <t>01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026</t>
         </is>
       </c>
       <c r="G341" t="inlineStr"/>
@@ -36296,7 +35800,7 @@
       <c r="W341" t="inlineStr"/>
       <c r="X341" t="inlineStr">
         <is>
-          <t>26/01/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026</t>
+          <t>01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026 - Tỷ lệ thực hiện: 01 trái phiếu nhận được 102.470.136,986 đồng. - Ngày thanh toán: 26/01/2026</t>
         </is>
       </c>
       <c r="Y341" t="n">
@@ -40492,16 +39996,8 @@
         </is>
       </c>
       <c r="J402" t="inlineStr"/>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr"/>
       <c r="M402" t="inlineStr"/>
       <c r="N402" t="inlineStr"/>
       <c r="O402" t="inlineStr"/>
@@ -40519,7 +40015,7 @@
         </is>
       </c>
       <c r="Y402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z402" t="n">
         <v>0</v>
@@ -40539,7 +40035,11 @@
       </c>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
       <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr"/>
@@ -40616,7 +40116,11 @@
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
       <c r="G404" t="inlineStr">
         <is>
           <t>Chứng quyền</t>
@@ -40629,16 +40133,8 @@
         </is>
       </c>
       <c r="J404" t="inlineStr"/>
-      <c r="K404" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
-      <c r="L404" t="inlineStr">
-        <is>
-          <t>08/01/2026</t>
-        </is>
-      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
       <c r="M404" t="inlineStr"/>
       <c r="N404" t="inlineStr"/>
       <c r="O404" t="inlineStr"/>
@@ -40656,9 +40152,4401 @@
         </is>
       </c>
       <c r="Y404" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr"/>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
+      <c r="O405" t="inlineStr"/>
+      <c r="P405" t="inlineStr"/>
+      <c r="Q405" t="inlineStr"/>
+      <c r="R405" t="inlineStr"/>
+      <c r="S405" t="inlineStr"/>
+      <c r="T405" t="inlineStr"/>
+      <c r="U405" t="inlineStr"/>
+      <c r="V405" t="inlineStr"/>
+      <c r="W405" t="inlineStr"/>
+      <c r="X405" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y405" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z405" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr"/>
+      <c r="O406" t="inlineStr"/>
+      <c r="P406" t="inlineStr"/>
+      <c r="Q406" t="inlineStr"/>
+      <c r="R406" t="inlineStr"/>
+      <c r="S406" t="inlineStr"/>
+      <c r="T406" t="inlineStr"/>
+      <c r="U406" t="inlineStr"/>
+      <c r="V406" t="inlineStr"/>
+      <c r="W406" t="inlineStr"/>
+      <c r="X406" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y406" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr"/>
+      <c r="O407" t="inlineStr"/>
+      <c r="P407" t="inlineStr"/>
+      <c r="Q407" t="inlineStr"/>
+      <c r="R407" t="inlineStr"/>
+      <c r="S407" t="inlineStr"/>
+      <c r="T407" t="inlineStr"/>
+      <c r="U407" t="inlineStr"/>
+      <c r="V407" t="inlineStr"/>
+      <c r="W407" t="inlineStr"/>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y407" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z407" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr"/>
+      <c r="O408" t="inlineStr"/>
+      <c r="P408" t="inlineStr"/>
+      <c r="Q408" t="inlineStr"/>
+      <c r="R408" t="inlineStr"/>
+      <c r="S408" t="inlineStr"/>
+      <c r="T408" t="inlineStr"/>
+      <c r="U408" t="inlineStr"/>
+      <c r="V408" t="inlineStr"/>
+      <c r="W408" t="inlineStr"/>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y408" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr"/>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr"/>
+      <c r="O409" t="inlineStr"/>
+      <c r="P409" t="inlineStr"/>
+      <c r="Q409" t="inlineStr"/>
+      <c r="R409" t="inlineStr"/>
+      <c r="S409" t="inlineStr"/>
+      <c r="T409" t="inlineStr"/>
+      <c r="U409" t="inlineStr"/>
+      <c r="V409" t="inlineStr"/>
+      <c r="W409" t="inlineStr"/>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y409" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z409" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr"/>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr"/>
+      <c r="O410" t="inlineStr"/>
+      <c r="P410" t="inlineStr"/>
+      <c r="Q410" t="inlineStr"/>
+      <c r="R410" t="inlineStr"/>
+      <c r="S410" t="inlineStr"/>
+      <c r="T410" t="inlineStr"/>
+      <c r="U410" t="inlineStr"/>
+      <c r="V410" t="inlineStr"/>
+      <c r="W410" t="inlineStr"/>
+      <c r="X410" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y410" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z410" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr"/>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr"/>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr"/>
+      <c r="O411" t="inlineStr"/>
+      <c r="P411" t="inlineStr"/>
+      <c r="Q411" t="inlineStr"/>
+      <c r="R411" t="inlineStr"/>
+      <c r="S411" t="inlineStr"/>
+      <c r="T411" t="inlineStr"/>
+      <c r="U411" t="inlineStr"/>
+      <c r="V411" t="inlineStr"/>
+      <c r="W411" t="inlineStr"/>
+      <c r="X411" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y411" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z411" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr"/>
+      <c r="O412" t="inlineStr"/>
+      <c r="P412" t="inlineStr"/>
+      <c r="Q412" t="inlineStr"/>
+      <c r="R412" t="inlineStr"/>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" t="inlineStr"/>
+      <c r="U412" t="inlineStr"/>
+      <c r="V412" t="inlineStr"/>
+      <c r="W412" t="inlineStr"/>
+      <c r="X412" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y412" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z412" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr"/>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr"/>
+      <c r="O413" t="inlineStr"/>
+      <c r="P413" t="inlineStr"/>
+      <c r="Q413" t="inlineStr"/>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="inlineStr"/>
+      <c r="T413" t="inlineStr"/>
+      <c r="U413" t="inlineStr"/>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" t="inlineStr"/>
+      <c r="X413" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y413" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z413" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr"/>
+      <c r="O414" t="inlineStr"/>
+      <c r="P414" t="inlineStr"/>
+      <c r="Q414" t="inlineStr"/>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="inlineStr"/>
+      <c r="T414" t="inlineStr"/>
+      <c r="U414" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" t="inlineStr"/>
+      <c r="X414" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y414" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z414" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr"/>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr"/>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr"/>
+      <c r="O415" t="inlineStr"/>
+      <c r="P415" t="inlineStr"/>
+      <c r="Q415" t="inlineStr"/>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="inlineStr"/>
+      <c r="T415" t="inlineStr"/>
+      <c r="U415" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" t="inlineStr"/>
+      <c r="X415" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y415" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z415" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr"/>
+      <c r="O416" t="inlineStr"/>
+      <c r="P416" t="inlineStr"/>
+      <c r="Q416" t="inlineStr"/>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="inlineStr"/>
+      <c r="T416" t="inlineStr"/>
+      <c r="U416" t="inlineStr"/>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" t="inlineStr"/>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y416" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z416" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr"/>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr"/>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr"/>
+      <c r="O417" t="inlineStr"/>
+      <c r="P417" t="inlineStr"/>
+      <c r="Q417" t="inlineStr"/>
+      <c r="R417" t="inlineStr"/>
+      <c r="S417" t="inlineStr"/>
+      <c r="T417" t="inlineStr"/>
+      <c r="U417" t="inlineStr"/>
+      <c r="V417" t="inlineStr"/>
+      <c r="W417" t="inlineStr"/>
+      <c r="X417" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y417" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr"/>
+      <c r="O418" t="inlineStr"/>
+      <c r="P418" t="inlineStr"/>
+      <c r="Q418" t="inlineStr"/>
+      <c r="R418" t="inlineStr"/>
+      <c r="S418" t="inlineStr"/>
+      <c r="T418" t="inlineStr"/>
+      <c r="U418" t="inlineStr"/>
+      <c r="V418" t="inlineStr"/>
+      <c r="W418" t="inlineStr"/>
+      <c r="X418" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y418" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z418" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr"/>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr"/>
+      <c r="O419" t="inlineStr"/>
+      <c r="P419" t="inlineStr"/>
+      <c r="Q419" t="inlineStr"/>
+      <c r="R419" t="inlineStr"/>
+      <c r="S419" t="inlineStr"/>
+      <c r="T419" t="inlineStr"/>
+      <c r="U419" t="inlineStr"/>
+      <c r="V419" t="inlineStr"/>
+      <c r="W419" t="inlineStr"/>
+      <c r="X419" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y419" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z419" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr"/>
+      <c r="O420" t="inlineStr"/>
+      <c r="P420" t="inlineStr"/>
+      <c r="Q420" t="inlineStr"/>
+      <c r="R420" t="inlineStr"/>
+      <c r="S420" t="inlineStr"/>
+      <c r="T420" t="inlineStr"/>
+      <c r="U420" t="inlineStr"/>
+      <c r="V420" t="inlineStr"/>
+      <c r="W420" t="inlineStr"/>
+      <c r="X420" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y420" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr"/>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="inlineStr"/>
+      <c r="O421" t="inlineStr"/>
+      <c r="P421" t="inlineStr"/>
+      <c r="Q421" t="inlineStr"/>
+      <c r="R421" t="inlineStr"/>
+      <c r="S421" t="inlineStr"/>
+      <c r="T421" t="inlineStr"/>
+      <c r="U421" t="inlineStr"/>
+      <c r="V421" t="inlineStr"/>
+      <c r="W421" t="inlineStr"/>
+      <c r="X421" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y421" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z421" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="inlineStr"/>
+      <c r="O422" t="inlineStr"/>
+      <c r="P422" t="inlineStr"/>
+      <c r="Q422" t="inlineStr"/>
+      <c r="R422" t="inlineStr"/>
+      <c r="S422" t="inlineStr"/>
+      <c r="T422" t="inlineStr"/>
+      <c r="U422" t="inlineStr"/>
+      <c r="V422" t="inlineStr"/>
+      <c r="W422" t="inlineStr"/>
+      <c r="X422" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y422" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z422" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr"/>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="inlineStr"/>
+      <c r="O423" t="inlineStr"/>
+      <c r="P423" t="inlineStr"/>
+      <c r="Q423" t="inlineStr"/>
+      <c r="R423" t="inlineStr"/>
+      <c r="S423" t="inlineStr"/>
+      <c r="T423" t="inlineStr"/>
+      <c r="U423" t="inlineStr"/>
+      <c r="V423" t="inlineStr"/>
+      <c r="W423" t="inlineStr"/>
+      <c r="X423" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y423" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z423" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr"/>
+      <c r="O424" t="inlineStr"/>
+      <c r="P424" t="inlineStr"/>
+      <c r="Q424" t="inlineStr"/>
+      <c r="R424" t="inlineStr"/>
+      <c r="S424" t="inlineStr"/>
+      <c r="T424" t="inlineStr"/>
+      <c r="U424" t="inlineStr"/>
+      <c r="V424" t="inlineStr"/>
+      <c r="W424" t="inlineStr"/>
+      <c r="X424" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y424" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr"/>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="inlineStr"/>
+      <c r="O425" t="inlineStr"/>
+      <c r="P425" t="inlineStr"/>
+      <c r="Q425" t="inlineStr"/>
+      <c r="R425" t="inlineStr"/>
+      <c r="S425" t="inlineStr"/>
+      <c r="T425" t="inlineStr"/>
+      <c r="U425" t="inlineStr"/>
+      <c r="V425" t="inlineStr"/>
+      <c r="W425" t="inlineStr"/>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y425" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr"/>
+      <c r="O426" t="inlineStr"/>
+      <c r="P426" t="inlineStr"/>
+      <c r="Q426" t="inlineStr"/>
+      <c r="R426" t="inlineStr"/>
+      <c r="S426" t="inlineStr"/>
+      <c r="T426" t="inlineStr"/>
+      <c r="U426" t="inlineStr"/>
+      <c r="V426" t="inlineStr"/>
+      <c r="W426" t="inlineStr"/>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y426" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr"/>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr"/>
+      <c r="O427" t="inlineStr"/>
+      <c r="P427" t="inlineStr"/>
+      <c r="Q427" t="inlineStr"/>
+      <c r="R427" t="inlineStr"/>
+      <c r="S427" t="inlineStr"/>
+      <c r="T427" t="inlineStr"/>
+      <c r="U427" t="inlineStr"/>
+      <c r="V427" t="inlineStr"/>
+      <c r="W427" t="inlineStr"/>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y427" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z427" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr"/>
+      <c r="O428" t="inlineStr"/>
+      <c r="P428" t="inlineStr"/>
+      <c r="Q428" t="inlineStr"/>
+      <c r="R428" t="inlineStr"/>
+      <c r="S428" t="inlineStr"/>
+      <c r="T428" t="inlineStr"/>
+      <c r="U428" t="inlineStr"/>
+      <c r="V428" t="inlineStr"/>
+      <c r="W428" t="inlineStr"/>
+      <c r="X428" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr"/>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
+      <c r="N429" t="inlineStr"/>
+      <c r="O429" t="inlineStr"/>
+      <c r="P429" t="inlineStr"/>
+      <c r="Q429" t="inlineStr"/>
+      <c r="R429" t="inlineStr"/>
+      <c r="S429" t="inlineStr"/>
+      <c r="T429" t="inlineStr"/>
+      <c r="U429" t="inlineStr"/>
+      <c r="V429" t="inlineStr"/>
+      <c r="W429" t="inlineStr"/>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y429" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
+      <c r="N430" t="inlineStr"/>
+      <c r="O430" t="inlineStr"/>
+      <c r="P430" t="inlineStr"/>
+      <c r="Q430" t="inlineStr"/>
+      <c r="R430" t="inlineStr"/>
+      <c r="S430" t="inlineStr"/>
+      <c r="T430" t="inlineStr"/>
+      <c r="U430" t="inlineStr"/>
+      <c r="V430" t="inlineStr"/>
+      <c r="W430" t="inlineStr"/>
+      <c r="X430" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y430" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z430" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr"/>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
+      <c r="N431" t="inlineStr"/>
+      <c r="O431" t="inlineStr"/>
+      <c r="P431" t="inlineStr"/>
+      <c r="Q431" t="inlineStr"/>
+      <c r="R431" t="inlineStr"/>
+      <c r="S431" t="inlineStr"/>
+      <c r="T431" t="inlineStr"/>
+      <c r="U431" t="inlineStr"/>
+      <c r="V431" t="inlineStr"/>
+      <c r="W431" t="inlineStr"/>
+      <c r="X431" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y431" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z431" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
+      <c r="N432" t="inlineStr"/>
+      <c r="O432" t="inlineStr"/>
+      <c r="P432" t="inlineStr"/>
+      <c r="Q432" t="inlineStr"/>
+      <c r="R432" t="inlineStr"/>
+      <c r="S432" t="inlineStr"/>
+      <c r="T432" t="inlineStr"/>
+      <c r="U432" t="inlineStr"/>
+      <c r="V432" t="inlineStr"/>
+      <c r="W432" t="inlineStr"/>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y432" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z432" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr"/>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
+      <c r="N433" t="inlineStr"/>
+      <c r="O433" t="inlineStr"/>
+      <c r="P433" t="inlineStr"/>
+      <c r="Q433" t="inlineStr"/>
+      <c r="R433" t="inlineStr"/>
+      <c r="S433" t="inlineStr"/>
+      <c r="T433" t="inlineStr"/>
+      <c r="U433" t="inlineStr"/>
+      <c r="V433" t="inlineStr"/>
+      <c r="W433" t="inlineStr"/>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y433" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z433" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="inlineStr"/>
+      <c r="O434" t="inlineStr"/>
+      <c r="P434" t="inlineStr"/>
+      <c r="Q434" t="inlineStr"/>
+      <c r="R434" t="inlineStr"/>
+      <c r="S434" t="inlineStr"/>
+      <c r="T434" t="inlineStr"/>
+      <c r="U434" t="inlineStr"/>
+      <c r="V434" t="inlineStr"/>
+      <c r="W434" t="inlineStr"/>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y434" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z434" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr"/>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
+      <c r="N435" t="inlineStr"/>
+      <c r="O435" t="inlineStr"/>
+      <c r="P435" t="inlineStr"/>
+      <c r="Q435" t="inlineStr"/>
+      <c r="R435" t="inlineStr"/>
+      <c r="S435" t="inlineStr"/>
+      <c r="T435" t="inlineStr"/>
+      <c r="U435" t="inlineStr"/>
+      <c r="V435" t="inlineStr"/>
+      <c r="W435" t="inlineStr"/>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y435" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z435" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
+      <c r="N436" t="inlineStr"/>
+      <c r="O436" t="inlineStr"/>
+      <c r="P436" t="inlineStr"/>
+      <c r="Q436" t="inlineStr"/>
+      <c r="R436" t="inlineStr"/>
+      <c r="S436" t="inlineStr"/>
+      <c r="T436" t="inlineStr"/>
+      <c r="U436" t="inlineStr"/>
+      <c r="V436" t="inlineStr"/>
+      <c r="W436" t="inlineStr"/>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr"/>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
+      <c r="N437" t="inlineStr"/>
+      <c r="O437" t="inlineStr"/>
+      <c r="P437" t="inlineStr"/>
+      <c r="Q437" t="inlineStr"/>
+      <c r="R437" t="inlineStr"/>
+      <c r="S437" t="inlineStr"/>
+      <c r="T437" t="inlineStr"/>
+      <c r="U437" t="inlineStr"/>
+      <c r="V437" t="inlineStr"/>
+      <c r="W437" t="inlineStr"/>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr"/>
+      <c r="O438" t="inlineStr"/>
+      <c r="P438" t="inlineStr"/>
+      <c r="Q438" t="inlineStr"/>
+      <c r="R438" t="inlineStr"/>
+      <c r="S438" t="inlineStr"/>
+      <c r="T438" t="inlineStr"/>
+      <c r="U438" t="inlineStr"/>
+      <c r="V438" t="inlineStr"/>
+      <c r="W438" t="inlineStr"/>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr"/>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="inlineStr"/>
+      <c r="O439" t="inlineStr"/>
+      <c r="P439" t="inlineStr"/>
+      <c r="Q439" t="inlineStr"/>
+      <c r="R439" t="inlineStr"/>
+      <c r="S439" t="inlineStr"/>
+      <c r="T439" t="inlineStr"/>
+      <c r="U439" t="inlineStr"/>
+      <c r="V439" t="inlineStr"/>
+      <c r="W439" t="inlineStr"/>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr"/>
+      <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr"/>
+      <c r="O440" t="inlineStr"/>
+      <c r="P440" t="inlineStr"/>
+      <c r="Q440" t="inlineStr"/>
+      <c r="R440" t="inlineStr"/>
+      <c r="S440" t="inlineStr"/>
+      <c r="T440" t="inlineStr"/>
+      <c r="U440" t="inlineStr"/>
+      <c r="V440" t="inlineStr"/>
+      <c r="W440" t="inlineStr"/>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr"/>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr"/>
+      <c r="O441" t="inlineStr"/>
+      <c r="P441" t="inlineStr"/>
+      <c r="Q441" t="inlineStr"/>
+      <c r="R441" t="inlineStr"/>
+      <c r="S441" t="inlineStr"/>
+      <c r="T441" t="inlineStr"/>
+      <c r="U441" t="inlineStr"/>
+      <c r="V441" t="inlineStr"/>
+      <c r="W441" t="inlineStr"/>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y441" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr"/>
+      <c r="O442" t="inlineStr"/>
+      <c r="P442" t="inlineStr"/>
+      <c r="Q442" t="inlineStr"/>
+      <c r="R442" t="inlineStr"/>
+      <c r="S442" t="inlineStr"/>
+      <c r="T442" t="inlineStr"/>
+      <c r="U442" t="inlineStr"/>
+      <c r="V442" t="inlineStr"/>
+      <c r="W442" t="inlineStr"/>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr"/>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr"/>
+      <c r="O443" t="inlineStr"/>
+      <c r="P443" t="inlineStr"/>
+      <c r="Q443" t="inlineStr"/>
+      <c r="R443" t="inlineStr"/>
+      <c r="S443" t="inlineStr"/>
+      <c r="T443" t="inlineStr"/>
+      <c r="U443" t="inlineStr"/>
+      <c r="V443" t="inlineStr"/>
+      <c r="W443" t="inlineStr"/>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr"/>
+      <c r="O444" t="inlineStr"/>
+      <c r="P444" t="inlineStr"/>
+      <c r="Q444" t="inlineStr"/>
+      <c r="R444" t="inlineStr"/>
+      <c r="S444" t="inlineStr"/>
+      <c r="T444" t="inlineStr"/>
+      <c r="U444" t="inlineStr"/>
+      <c r="V444" t="inlineStr"/>
+      <c r="W444" t="inlineStr"/>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y444" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr"/>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr"/>
+      <c r="O445" t="inlineStr"/>
+      <c r="P445" t="inlineStr"/>
+      <c r="Q445" t="inlineStr"/>
+      <c r="R445" t="inlineStr"/>
+      <c r="S445" t="inlineStr"/>
+      <c r="T445" t="inlineStr"/>
+      <c r="U445" t="inlineStr"/>
+      <c r="V445" t="inlineStr"/>
+      <c r="W445" t="inlineStr"/>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr"/>
+      <c r="N446" t="inlineStr"/>
+      <c r="O446" t="inlineStr"/>
+      <c r="P446" t="inlineStr"/>
+      <c r="Q446" t="inlineStr"/>
+      <c r="R446" t="inlineStr"/>
+      <c r="S446" t="inlineStr"/>
+      <c r="T446" t="inlineStr"/>
+      <c r="U446" t="inlineStr"/>
+      <c r="V446" t="inlineStr"/>
+      <c r="W446" t="inlineStr"/>
+      <c r="X446" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr"/>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr"/>
+      <c r="N447" t="inlineStr"/>
+      <c r="O447" t="inlineStr"/>
+      <c r="P447" t="inlineStr"/>
+      <c r="Q447" t="inlineStr"/>
+      <c r="R447" t="inlineStr"/>
+      <c r="S447" t="inlineStr"/>
+      <c r="T447" t="inlineStr"/>
+      <c r="U447" t="inlineStr"/>
+      <c r="V447" t="inlineStr"/>
+      <c r="W447" t="inlineStr"/>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr"/>
+      <c r="N448" t="inlineStr"/>
+      <c r="O448" t="inlineStr"/>
+      <c r="P448" t="inlineStr"/>
+      <c r="Q448" t="inlineStr"/>
+      <c r="R448" t="inlineStr"/>
+      <c r="S448" t="inlineStr"/>
+      <c r="T448" t="inlineStr"/>
+      <c r="U448" t="inlineStr"/>
+      <c r="V448" t="inlineStr"/>
+      <c r="W448" t="inlineStr"/>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y448" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z448" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr"/>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr"/>
+      <c r="N449" t="inlineStr"/>
+      <c r="O449" t="inlineStr"/>
+      <c r="P449" t="inlineStr"/>
+      <c r="Q449" t="inlineStr"/>
+      <c r="R449" t="inlineStr"/>
+      <c r="S449" t="inlineStr"/>
+      <c r="T449" t="inlineStr"/>
+      <c r="U449" t="inlineStr"/>
+      <c r="V449" t="inlineStr"/>
+      <c r="W449" t="inlineStr"/>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y449" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z449" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr"/>
+      <c r="N450" t="inlineStr"/>
+      <c r="O450" t="inlineStr"/>
+      <c r="P450" t="inlineStr"/>
+      <c r="Q450" t="inlineStr"/>
+      <c r="R450" t="inlineStr"/>
+      <c r="S450" t="inlineStr"/>
+      <c r="T450" t="inlineStr"/>
+      <c r="U450" t="inlineStr"/>
+      <c r="V450" t="inlineStr"/>
+      <c r="W450" t="inlineStr"/>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y450" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z450" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr"/>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr"/>
+      <c r="I451" t="inlineStr"/>
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="inlineStr"/>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr"/>
+      <c r="N451" t="inlineStr"/>
+      <c r="O451" t="inlineStr"/>
+      <c r="P451" t="inlineStr"/>
+      <c r="Q451" t="inlineStr"/>
+      <c r="R451" t="inlineStr"/>
+      <c r="S451" t="inlineStr"/>
+      <c r="T451" t="inlineStr"/>
+      <c r="U451" t="inlineStr"/>
+      <c r="V451" t="inlineStr"/>
+      <c r="W451" t="inlineStr"/>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y451" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z451" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr"/>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr"/>
+      <c r="N452" t="inlineStr"/>
+      <c r="O452" t="inlineStr"/>
+      <c r="P452" t="inlineStr"/>
+      <c r="Q452" t="inlineStr"/>
+      <c r="R452" t="inlineStr"/>
+      <c r="S452" t="inlineStr"/>
+      <c r="T452" t="inlineStr"/>
+      <c r="U452" t="inlineStr"/>
+      <c r="V452" t="inlineStr"/>
+      <c r="W452" t="inlineStr"/>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y452" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z452" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr"/>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr"/>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr"/>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr"/>
+      <c r="N453" t="inlineStr"/>
+      <c r="O453" t="inlineStr"/>
+      <c r="P453" t="inlineStr"/>
+      <c r="Q453" t="inlineStr"/>
+      <c r="R453" t="inlineStr"/>
+      <c r="S453" t="inlineStr"/>
+      <c r="T453" t="inlineStr"/>
+      <c r="U453" t="inlineStr"/>
+      <c r="V453" t="inlineStr"/>
+      <c r="W453" t="inlineStr"/>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y453" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z453" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr"/>
+      <c r="N454" t="inlineStr"/>
+      <c r="O454" t="inlineStr"/>
+      <c r="P454" t="inlineStr"/>
+      <c r="Q454" t="inlineStr"/>
+      <c r="R454" t="inlineStr"/>
+      <c r="S454" t="inlineStr"/>
+      <c r="T454" t="inlineStr"/>
+      <c r="U454" t="inlineStr"/>
+      <c r="V454" t="inlineStr"/>
+      <c r="W454" t="inlineStr"/>
+      <c r="X454" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y454" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z454" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr"/>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr"/>
+      <c r="N455" t="inlineStr"/>
+      <c r="O455" t="inlineStr"/>
+      <c r="P455" t="inlineStr"/>
+      <c r="Q455" t="inlineStr"/>
+      <c r="R455" t="inlineStr"/>
+      <c r="S455" t="inlineStr"/>
+      <c r="T455" t="inlineStr"/>
+      <c r="U455" t="inlineStr"/>
+      <c r="V455" t="inlineStr"/>
+      <c r="W455" t="inlineStr"/>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y455" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z455" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr"/>
+      <c r="N456" t="inlineStr"/>
+      <c r="O456" t="inlineStr"/>
+      <c r="P456" t="inlineStr"/>
+      <c r="Q456" t="inlineStr"/>
+      <c r="R456" t="inlineStr"/>
+      <c r="S456" t="inlineStr"/>
+      <c r="T456" t="inlineStr"/>
+      <c r="U456" t="inlineStr"/>
+      <c r="V456" t="inlineStr"/>
+      <c r="W456" t="inlineStr"/>
+      <c r="X456" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y456" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z456" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr"/>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr"/>
+      <c r="N457" t="inlineStr"/>
+      <c r="O457" t="inlineStr"/>
+      <c r="P457" t="inlineStr"/>
+      <c r="Q457" t="inlineStr"/>
+      <c r="R457" t="inlineStr"/>
+      <c r="S457" t="inlineStr"/>
+      <c r="T457" t="inlineStr"/>
+      <c r="U457" t="inlineStr"/>
+      <c r="V457" t="inlineStr"/>
+      <c r="W457" t="inlineStr"/>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y457" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z457" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr"/>
+      <c r="N458" t="inlineStr"/>
+      <c r="O458" t="inlineStr"/>
+      <c r="P458" t="inlineStr"/>
+      <c r="Q458" t="inlineStr"/>
+      <c r="R458" t="inlineStr"/>
+      <c r="S458" t="inlineStr"/>
+      <c r="T458" t="inlineStr"/>
+      <c r="U458" t="inlineStr"/>
+      <c r="V458" t="inlineStr"/>
+      <c r="W458" t="inlineStr"/>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y458" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z458" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr"/>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr"/>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr"/>
+      <c r="N459" t="inlineStr"/>
+      <c r="O459" t="inlineStr"/>
+      <c r="P459" t="inlineStr"/>
+      <c r="Q459" t="inlineStr"/>
+      <c r="R459" t="inlineStr"/>
+      <c r="S459" t="inlineStr"/>
+      <c r="T459" t="inlineStr"/>
+      <c r="U459" t="inlineStr"/>
+      <c r="V459" t="inlineStr"/>
+      <c r="W459" t="inlineStr"/>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y459" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z459" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr"/>
+      <c r="N460" t="inlineStr"/>
+      <c r="O460" t="inlineStr"/>
+      <c r="P460" t="inlineStr"/>
+      <c r="Q460" t="inlineStr"/>
+      <c r="R460" t="inlineStr"/>
+      <c r="S460" t="inlineStr"/>
+      <c r="T460" t="inlineStr"/>
+      <c r="U460" t="inlineStr"/>
+      <c r="V460" t="inlineStr"/>
+      <c r="W460" t="inlineStr"/>
+      <c r="X460" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y460" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z460" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr"/>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
+      <c r="N461" t="inlineStr"/>
+      <c r="O461" t="inlineStr"/>
+      <c r="P461" t="inlineStr"/>
+      <c r="Q461" t="inlineStr"/>
+      <c r="R461" t="inlineStr"/>
+      <c r="S461" t="inlineStr"/>
+      <c r="T461" t="inlineStr"/>
+      <c r="U461" t="inlineStr"/>
+      <c r="V461" t="inlineStr"/>
+      <c r="W461" t="inlineStr"/>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y461" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z461" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr"/>
+      <c r="N462" t="inlineStr"/>
+      <c r="O462" t="inlineStr"/>
+      <c r="P462" t="inlineStr"/>
+      <c r="Q462" t="inlineStr"/>
+      <c r="R462" t="inlineStr"/>
+      <c r="S462" t="inlineStr"/>
+      <c r="T462" t="inlineStr"/>
+      <c r="U462" t="inlineStr"/>
+      <c r="V462" t="inlineStr"/>
+      <c r="W462" t="inlineStr"/>
+      <c r="X462" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y462" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z462" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr"/>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr"/>
+      <c r="N463" t="inlineStr"/>
+      <c r="O463" t="inlineStr"/>
+      <c r="P463" t="inlineStr"/>
+      <c r="Q463" t="inlineStr"/>
+      <c r="R463" t="inlineStr"/>
+      <c r="S463" t="inlineStr"/>
+      <c r="T463" t="inlineStr"/>
+      <c r="U463" t="inlineStr"/>
+      <c r="V463" t="inlineStr"/>
+      <c r="W463" t="inlineStr"/>
+      <c r="X463" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y463" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z463" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
+      <c r="N464" t="inlineStr"/>
+      <c r="O464" t="inlineStr"/>
+      <c r="P464" t="inlineStr"/>
+      <c r="Q464" t="inlineStr"/>
+      <c r="R464" t="inlineStr"/>
+      <c r="S464" t="inlineStr"/>
+      <c r="T464" t="inlineStr"/>
+      <c r="U464" t="inlineStr"/>
+      <c r="V464" t="inlineStr"/>
+      <c r="W464" t="inlineStr"/>
+      <c r="X464" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y464" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z464" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr"/>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:08</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" t="inlineStr"/>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr"/>
+      <c r="N465" t="inlineStr"/>
+      <c r="O465" t="inlineStr"/>
+      <c r="P465" t="inlineStr"/>
+      <c r="Q465" t="inlineStr"/>
+      <c r="R465" t="inlineStr"/>
+      <c r="S465" t="inlineStr"/>
+      <c r="T465" t="inlineStr"/>
+      <c r="U465" t="inlineStr"/>
+      <c r="V465" t="inlineStr"/>
+      <c r="W465" t="inlineStr"/>
+      <c r="X465" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y465" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z465" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36:10</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr"/>
+      <c r="N466" t="inlineStr"/>
+      <c r="O466" t="inlineStr"/>
+      <c r="P466" t="inlineStr"/>
+      <c r="Q466" t="inlineStr"/>
+      <c r="R466" t="inlineStr"/>
+      <c r="S466" t="inlineStr"/>
+      <c r="T466" t="inlineStr"/>
+      <c r="U466" t="inlineStr"/>
+      <c r="V466" t="inlineStr"/>
+      <c r="W466" t="inlineStr"/>
+      <c r="X466" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y466" t="n">
         <v>1</v>
       </c>
-      <c r="Z404" t="n">
+      <c r="Z466" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr"/>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:44</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/193591</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
+      <c r="N467" t="inlineStr"/>
+      <c r="O467" t="inlineStr"/>
+      <c r="P467" t="inlineStr"/>
+      <c r="Q467" t="inlineStr"/>
+      <c r="R467" t="inlineStr"/>
+      <c r="S467" t="inlineStr"/>
+      <c r="T467" t="inlineStr"/>
+      <c r="U467" t="inlineStr"/>
+      <c r="V467" t="inlineStr"/>
+      <c r="W467" t="inlineStr"/>
+      <c r="X467" t="inlineStr">
+        <is>
+          <t>Excel Link</t>
+        </is>
+      </c>
+      <c r="Y467" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z467" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>10/01/2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:03:48</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>https://www.vsd.vn/vi/ad/190919</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>CFPT2505: Hủy đợt chốt danh sách thực hiện chứng quyền
+Cập nhật ngày 10/01/2026 - 08:47:41
+Tiếp theo Thông báo số 4599/TB-VSDC ngày 19/12/2025 về ngày đăng ký cuối cùng để thực hiện chứng quyền, Tổng công ty Lưu ký và Bù trừ chứng khoán Việt Nam (VSDC) thông báo về việc hủy đợt chốt danh sách thực hiện chứng quyền như sau:
+Tên tổ chức đăng ký chứng khoán:
+Công ty cổ phần Chứng khoán BIDV
+Tên chứng quyền:
+Chứng quyền FPT/BSC/C/12M/EU/Cash/2024-01
+Mã chứng quyền:
+CFPT2505
+Mã ISIN:
+VN0CFPT25051
+Thị trường giao dịch:
+HOSE
+Loại chứng quyền:
+Mua
+Thời hạn:
+12 tháng
+Ngày phát hành:
+Ngày đáo hạn:
+09/01/2026
+Ngày đăng ký cuối cùng:
+09/01/2026
+Lý do mục đích:
+Hủy đợt chốt danh sách thực hiện chứng quyền
+Căn cứ vào công văn của CTCP Chứng khoán BIDV về việc chứng quyền không có lãi, VSDC thông báo hủy bỏ đợt chốt danh sách người sở hữu chứng quyền tại Thông báo số 4599/TB-VSDC.
+Đề nghị các Thành viên lưu ký (TVLK) thông báo đến từng nhà đầu tư lưu ký chứng quyền CFPT2505 tại TVLK./.</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Chứng quyền</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>VN0CFPT25051</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr"/>
+      <c r="N468" t="inlineStr"/>
+      <c r="O468" t="inlineStr"/>
+      <c r="P468" t="inlineStr"/>
+      <c r="Q468" t="inlineStr"/>
+      <c r="R468" t="inlineStr"/>
+      <c r="S468" t="inlineStr"/>
+      <c r="T468" t="inlineStr"/>
+      <c r="U468" t="inlineStr"/>
+      <c r="V468" t="inlineStr"/>
+      <c r="W468" t="inlineStr"/>
+      <c r="X468" t="inlineStr">
+        <is>
+          <t>Hủy đợt chốt danh sách thực hiện chứng quyền</t>
+        </is>
+      </c>
+      <c r="Y468" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z468" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/vsd_records.xlsx
+++ b/data/vsd_records.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:21</t>
+          <t>15/06/2026 17:52:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:22</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:22</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:22</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:22</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:22</t>
+          <t>15/06/2026 17:52:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:22</t>
+          <t>15/06/2026 17:52:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:22</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:22</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:22</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:23</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:37</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:24</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:38</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:25</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:39</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:26</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:40</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:27</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:41</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12125,7 +12125,11 @@
 CTCP tập đoàn cơ khí Công nghệ cao Siba và các tổ chức, cá nhân tham gia vào quá trình lập hồ sơ, tài liệu thực hiện quyền phải chịu trách nhiệm trước pháp luật về tính hợp pháp, chính xác, trung thực và đầy đủ của hồ sơ; Tổ chức, cá nhân tham gia vào xác nhận hồ sơ, tài liệu phải chịu trách nhiệm trước pháp luật trong phạm vi liên quan đến hồ sơ, tài liệu đó theo quy định tại khoản 1 Điều 11a Luật Chứng khoán số 54/2019/QH14 ngày 26/11/2019 được bổ sung tại khoản 4 Điều 1 Luật số 56/2024/QH15 ngày 29/11/2024./.</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>SBG</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>Thực hiện quyền nhận cổ tức bằng cổ phiếu</t>
@@ -12146,11 +12150,7 @@
           <t>VN000000SBG1</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>SBG</t>
-        </is>
-      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>26/06/2026</t>
@@ -12163,7 +12163,11 @@
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -12178,7 +12182,7 @@
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Thực hiện quyền nhận cổ tức bằng cổ phiếu - a. Thực hiện quyền nhận cổ tức bằng cổ phiếu - Tỷ lệ thực hiện: 100:20 (Mỗi cổ đông nắm giữ 100 cổ phiếu sẽ được nhận thêm 20 cổ phiếu mới) - Phương án làm tròn, phương án xử lý cổ phiếu lẻ (nếu có): Số lượng cổ phiếu phát hành thêm cho cổ đông hiện hữu sẽ được làm tròn xuống đến hàng đơn vị, phần cổ phiếu lẻ phát sinh (nếu có) sẽ bị hủy bỏ. - Ví dụ: Tại ngày chốt danh sách cổ đông để thực hiện quyền, cổ đông A sở hữu 2.026 cổ phiếu SBG. Cổ đông A sẽ nhận được thêm: (2.026/100)*20= 405,2 cổ phiếu SBG. Theo nguyên tắc làm tròn, cổ đông A nhận được 405 cổ phiếu SBG, phần lẻ là 0,2 cổ phiếu sẽ bị hủy bỏ - Địa điểm thực hiện: + Đối với chứng khoán lưu ký: Người sở hữu chứng khoán nhận cổ tức bằng cổ phiếu tại các thành viên lưu ký nơi mở tài khoản lưu ký, tổ chức mở tài khoản trực tiếp tại VSDC. + Đối với chứng khoán chưa lưu ký: Người sở hữu chứng khoán làm thủ tục nhận cổ tức bằng cổ phiếu tại văn phòng đại diện của Công ty Cổ phần Tập đoàn Cơ khí Công nghệ cao Siba - Tầng 7, Tòa nhà Vista Tower, 628C đường Võ Nguyên Giáp, Phường An Khánh, Thành phố Hồ Chí Minh và xuất trình căn cước công dân/căn cước.</t>
+          <t>Thực hiện quyền nhận cổ tức bằng cổ phiếu - Tỷ lệ thực hiện: 100:20 (Mỗi cổ đông nắm giữ 100 cổ phiếu sẽ được nhận thêm 20 cổ phiếu mới) - Thời gian thực hiện: Dự kiến trong tháng 7/2026. Thời gian cụ thể sẽ thông báo đến cổ đông trong Phiếu lấy ý kiến cổ đông bằng văn bản.</t>
         </is>
       </c>
       <c r="Y88" t="n">
@@ -12209,7 +12213,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12259,7 +12263,11 @@
 CTCP tập đoàn cơ khí Công nghệ cao Siba và các tổ chức, cá nhân tham gia vào quá trình lập hồ sơ, tài liệu thực hiện quyền phải chịu trách nhiệm trước pháp luật về tính hợp pháp, chính xác, trung thực và đầy đủ của hồ sơ; Tổ chức, cá nhân tham gia vào xác nhận hồ sơ, tài liệu phải chịu trách nhiệm trước pháp luật trong phạm vi liên quan đến hồ sơ, tài liệu đó theo quy định tại khoản 1 Điều 11a Luật Chứng khoán số 54/2019/QH14 ngày 26/11/2019 được bổ sung tại khoản 4 Điều 1 Luật số 56/2024/QH15 ngày 29/11/2024./.</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SBG</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>Thực hiện lấy ý kiến cổ đông bằng văn bản lần 1 năm 2026</t>
@@ -12276,11 +12284,7 @@
           <t>VN000000SBG1</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>SBG</t>
-        </is>
-      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>26/06/2026</t>
@@ -12343,7 +12347,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12477,7 +12481,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:28</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -12613,7 +12617,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -12738,7 +12742,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12872,7 +12876,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -13021,7 +13025,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -13170,7 +13174,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -13311,7 +13315,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -13452,7 +13456,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:42</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -13593,7 +13597,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -13734,7 +13738,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -13869,7 +13873,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -14038,7 +14042,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -14161,7 +14165,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -14286,7 +14290,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -14426,7 +14430,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -14564,7 +14568,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -14703,7 +14707,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -14822,7 +14826,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:29</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -14956,7 +14960,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -15086,7 +15090,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -15221,7 +15225,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -15319,7 +15323,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -15417,7 +15421,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -15515,7 +15519,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:43</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -15613,7 +15617,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -15738,7 +15742,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -15836,7 +15840,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -15933,7 +15937,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -16031,7 +16035,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -16161,7 +16165,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:30</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -16295,7 +16299,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -16425,7 +16429,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -16555,7 +16559,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -16689,7 +16693,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -16835,7 +16839,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -16981,7 +16985,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:44</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -17127,7 +17131,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -17273,7 +17277,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -17419,7 +17423,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -17565,7 +17569,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -17711,7 +17715,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -17857,7 +17861,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -18003,7 +18007,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:31</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -18149,7 +18153,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -18295,7 +18299,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -18441,7 +18445,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -18587,7 +18591,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -18691,7 +18695,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -18795,7 +18799,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -18872,7 +18876,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:45</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -19011,7 +19015,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -19150,7 +19154,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -19289,7 +19293,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -19428,7 +19432,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -19567,7 +19571,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -19705,7 +19709,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -19835,7 +19839,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -19965,7 +19969,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:32</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -20095,7 +20099,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -20225,7 +20229,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -20355,7 +20359,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -20453,7 +20457,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -20588,7 +20592,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:46</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -20714,7 +20718,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -20842,7 +20846,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -20971,7 +20975,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -21101,7 +21105,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -21231,7 +21235,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -21360,7 +21364,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -21490,7 +21494,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -21620,7 +21624,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:33</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -21750,7 +21754,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -21879,7 +21883,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -22008,7 +22012,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -22137,7 +22141,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -22271,7 +22275,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:47</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -22398,7 +22402,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -22525,7 +22529,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -22655,7 +22659,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -22780,7 +22784,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -22910,7 +22914,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -22979,7 +22983,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -23090,7 +23094,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:34</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -23170,7 +23174,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -23278,7 +23282,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -23417,7 +23421,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -23532,7 +23536,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -23647,7 +23651,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -23750,7 +23754,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -23853,7 +23857,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:48</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -23956,7 +23960,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -24059,7 +24063,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -24185,7 +24189,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -24320,7 +24324,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -24418,7 +24422,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -24550,7 +24554,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:35</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -24675,7 +24679,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -24805,7 +24809,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -24935,7 +24939,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -25065,7 +25069,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -25207,7 +25211,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -25349,7 +25353,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -25482,7 +25486,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -25616,7 +25620,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:49</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -25750,7 +25754,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -25876,7 +25880,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -26010,7 +26014,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -26135,7 +26139,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -26269,7 +26273,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -26408,7 +26412,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -26547,7 +26551,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -26636,7 +26640,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:36</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -26726,7 +26730,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:37</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -26864,7 +26868,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:37</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -27003,7 +27007,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:37</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -27142,7 +27146,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:37</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -27272,7 +27276,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:37</t>
+          <t>15/06/2026 17:52:50</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -27406,7 +27410,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:37</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -27540,7 +27544,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:37</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -27679,7 +27683,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:37</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -27784,7 +27788,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -27882,7 +27886,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:37</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -27980,7 +27984,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -28103,7 +28107,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -28233,7 +28237,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -28363,7 +28367,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -28486,7 +28490,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -28616,7 +28620,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -28739,7 +28743,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -28869,7 +28873,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:51</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -28999,7 +29003,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -29129,7 +29133,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -29260,7 +29264,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -29394,7 +29398,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -29528,7 +29532,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -29662,7 +29666,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:38</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -29798,7 +29802,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:39</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -29934,7 +29938,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:39</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -30070,7 +30074,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:39</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -30205,7 +30209,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:39</t>
+          <t>15/06/2026 17:52:53</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -30339,7 +30343,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:39</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -30473,7 +30477,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:39</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -30602,7 +30606,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>15/06/2026 16:55:39</t>
+          <t>15/06/2026 17:52:52</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
